--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/B1_resumo_estabelecimentos.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/B1_resumo_estabelecimentos.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'estabelecimentos'!$A$1:$AP$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'por_capital'!$A$1:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'cesta'!$A$1:$W$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'cesta'!$A$1:$W$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'dicionario'!$A$1:$E$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -908,15 +908,15 @@
         </is>
       </c>
       <c r="AJ2" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A2,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A2,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK2" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A2,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A2,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL2" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A2,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A2,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM2" s="9" t="n">
@@ -1063,15 +1063,15 @@
         </is>
       </c>
       <c r="AJ3" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A3,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A3,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK3" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A3,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A3,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL3" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A3,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A3,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM3" s="9" t="n">
@@ -1214,15 +1214,15 @@
       <c r="AH4" s="9" t="n"/>
       <c r="AI4" s="9" t="n"/>
       <c r="AJ4" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A4,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A4,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK4" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A4,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A4,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL4" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A4,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A4,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM4" s="9" t="n"/>
@@ -1363,15 +1363,15 @@
         </is>
       </c>
       <c r="AJ5" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A5,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A5,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK5" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A5,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A5,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL5" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A5,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A5,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM5" s="9" t="n">
@@ -1520,19 +1520,25 @@
       <c r="AH6" s="9" t="n"/>
       <c r="AI6" s="9" t="n"/>
       <c r="AJ6" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A6,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A6,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK6" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A6,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A6,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL6" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A6,cesta!$A$2:$A$34,0)),"")</f>
-        <v/>
-      </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A6,cesta!$A$2:$A$37,0)),"")</f>
+        <v/>
+      </c>
+      <c r="AM6" s="9" t="n">
+        <v>362</v>
+      </c>
+      <c r="AN6" s="9" t="inlineStr">
+        <is>
+          <t>acervodejogos</t>
+        </is>
+      </c>
       <c r="AO6" s="9" t="n">
         <v>10</v>
       </c>
@@ -1673,15 +1679,15 @@
         </is>
       </c>
       <c r="AJ7" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A7,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A7,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK7" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A7,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A7,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL7" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A7,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A7,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
@@ -1830,15 +1836,15 @@
         </is>
       </c>
       <c r="AJ8" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A8,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A8,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK8" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A8,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A8,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL8" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A8,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A8,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM8" s="9" t="n">
@@ -1997,15 +2003,15 @@
         </is>
       </c>
       <c r="AJ9" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A9,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A9,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK9" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A9,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A9,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL9" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A9,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A9,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM9" s="9" t="n"/>
@@ -2140,15 +2146,15 @@
       <c r="AH10" s="9" t="n"/>
       <c r="AI10" s="9" t="n"/>
       <c r="AJ10" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A10,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A10,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK10" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A10,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A10,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL10" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A10,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A10,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM10" s="9" t="n"/>
@@ -2297,15 +2303,15 @@
         </is>
       </c>
       <c r="AJ11" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A11,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A11,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK11" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A11,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A11,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL11" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A11,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A11,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM11" s="9" t="n"/>
@@ -2454,15 +2460,15 @@
         </is>
       </c>
       <c r="AJ12" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A12,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A12,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK12" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A12,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A12,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL12" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A12,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A12,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM12" s="9" t="n">
@@ -2617,15 +2623,15 @@
         </is>
       </c>
       <c r="AJ13" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A13,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A13,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK13" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A13,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A13,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL13" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A13,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A13,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM13" s="9" t="n">
@@ -2780,15 +2786,15 @@
         </is>
       </c>
       <c r="AJ14" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A14,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A14,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK14" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A14,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A14,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL14" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A14,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A14,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM14" s="9" t="n"/>
@@ -2929,15 +2935,15 @@
         </is>
       </c>
       <c r="AJ15" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A15,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A15,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK15" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A15,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A15,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL15" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A15,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A15,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM15" s="9" t="n">
@@ -3090,15 +3096,15 @@
         </is>
       </c>
       <c r="AJ16" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A16,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A16,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK16" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A16,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A16,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL16" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A16,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A16,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM16" s="9" t="n"/>
@@ -3239,15 +3245,15 @@
       <c r="AH17" s="9" t="n"/>
       <c r="AI17" s="9" t="n"/>
       <c r="AJ17" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A17,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A17,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK17" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A17,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A17,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL17" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A17,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A17,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM17" s="9" t="n">
@@ -3382,15 +3388,15 @@
       <c r="AH18" s="9" t="n"/>
       <c r="AI18" s="9" t="n"/>
       <c r="AJ18" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A18,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A18,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK18" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A18,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A18,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL18" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A18,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A18,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM18" s="9" t="n"/>
@@ -3527,15 +3533,15 @@
       <c r="AH19" s="9" t="n"/>
       <c r="AI19" s="9" t="n"/>
       <c r="AJ19" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A19,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A19,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK19" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A19,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A19,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL19" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A19,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A19,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM19" s="9" t="n"/>
@@ -3680,15 +3686,15 @@
       <c r="AH20" s="9" t="n"/>
       <c r="AI20" s="9" t="n"/>
       <c r="AJ20" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A20,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A20,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK20" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A20,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A20,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL20" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A20,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A20,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM20" s="9" t="n"/>
@@ -3822,18 +3828,24 @@
         <v>21</v>
       </c>
       <c r="AG21" s="9" t="n"/>
-      <c r="AH21" s="9" t="n"/>
-      <c r="AI21" s="9" t="n"/>
+      <c r="AH21" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI21" s="9" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="AJ21" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A21,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A21,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK21" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A21,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A21,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL21" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A21,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A21,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM21" s="9" t="n"/>
@@ -3982,15 +3994,15 @@
         </is>
       </c>
       <c r="AJ22" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A22,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A22,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK22" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A22,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A22,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL22" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A22,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A22,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM22" s="9" t="n">
@@ -4147,15 +4159,15 @@
         </is>
       </c>
       <c r="AJ23" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A23,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A23,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK23" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A23,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A23,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL23" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A23,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A23,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM23" s="9" t="n"/>
@@ -4296,15 +4308,15 @@
         </is>
       </c>
       <c r="AJ24" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A24,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A24,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK24" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A24,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A24,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL24" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A24,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A24,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM24" s="9" t="n">
@@ -4457,15 +4469,15 @@
       <c r="AH25" s="9" t="n"/>
       <c r="AI25" s="9" t="n"/>
       <c r="AJ25" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A25,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A25,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK25" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A25,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A25,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL25" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A25,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A25,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM25" s="9" t="n"/>
@@ -4610,15 +4622,15 @@
       <c r="AH26" s="9" t="n"/>
       <c r="AI26" s="9" t="n"/>
       <c r="AJ26" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A26,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A26,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK26" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A26,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A26,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL26" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A26,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A26,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM26" s="9" t="n">
@@ -4775,15 +4787,15 @@
         </is>
       </c>
       <c r="AJ27" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A27,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A27,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK27" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A27,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A27,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL27" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A27,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A27,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM27" s="9" t="n"/>
@@ -4926,15 +4938,15 @@
         </is>
       </c>
       <c r="AJ28" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A28,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A28,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK28" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A28,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A28,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL28" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A28,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A28,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM28" s="9" t="n">
@@ -5077,15 +5089,15 @@
         </is>
       </c>
       <c r="AJ29" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A29,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A29,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK29" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A29,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A29,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL29" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A29,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A29,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM29" s="9" t="n">
@@ -5226,15 +5238,15 @@
       <c r="AH30" s="9" t="n"/>
       <c r="AI30" s="9" t="n"/>
       <c r="AJ30" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A30,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A30,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK30" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A30,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A30,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL30" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A30,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A30,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM30" s="9" t="n"/>
@@ -5379,15 +5391,15 @@
         </is>
       </c>
       <c r="AJ31" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A31,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A31,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK31" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A31,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A31,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL31" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A31,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A31,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM31" s="9" t="n">
@@ -5536,15 +5548,15 @@
       <c r="AH32" s="9" t="n"/>
       <c r="AI32" s="9" t="n"/>
       <c r="AJ32" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A32,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A32,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK32" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A32,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A32,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL32" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A32,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A32,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM32" s="9" t="n"/>
@@ -5683,15 +5695,15 @@
       <c r="AH33" s="9" t="n"/>
       <c r="AI33" s="9" t="n"/>
       <c r="AJ33" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A33,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A33,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK33" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A33,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A33,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL33" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A33,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A33,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM33" s="9" t="n"/>
@@ -5826,15 +5838,15 @@
       <c r="AH34" s="9" t="n"/>
       <c r="AI34" s="9" t="n"/>
       <c r="AJ34" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A34,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A34,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK34" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A34,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A34,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL34" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A34,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A34,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM34" s="9" t="n">
@@ -5989,15 +6001,15 @@
         </is>
       </c>
       <c r="AJ35" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A35,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A35,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK35" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A35,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A35,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL35" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A35,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A35,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM35" s="9" t="n">
@@ -6148,15 +6160,15 @@
         </is>
       </c>
       <c r="AJ36" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A36,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A36,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK36" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A36,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A36,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL36" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A36,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A36,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM36" s="9" t="n">
@@ -6311,15 +6323,15 @@
         </is>
       </c>
       <c r="AJ37" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A37,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A37,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK37" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A37,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A37,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL37" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A37,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A37,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM37" s="9" t="n">
@@ -6458,15 +6470,15 @@
       <c r="AH38" s="9" t="n"/>
       <c r="AI38" s="9" t="n"/>
       <c r="AJ38" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A38,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A38,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK38" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A38,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A38,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL38" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A38,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A38,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM38" s="9" t="n"/>
@@ -6601,15 +6613,15 @@
         </is>
       </c>
       <c r="AJ39" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A39,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A39,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK39" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A39,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A39,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL39" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A39,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A39,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM39" s="9" t="n"/>
@@ -6754,15 +6766,15 @@
         </is>
       </c>
       <c r="AJ40" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A40,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A40,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK40" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A40,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A40,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL40" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A40,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A40,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM40" s="9" t="n">
@@ -6913,15 +6925,15 @@
         </is>
       </c>
       <c r="AJ41" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A41,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A41,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK41" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A41,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A41,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL41" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A41,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A41,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM41" s="9" t="n"/>
@@ -7066,15 +7078,15 @@
         </is>
       </c>
       <c r="AJ42" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A42,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A42,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK42" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A42,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A42,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL42" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A42,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A42,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM42" s="9" t="n">
@@ -7225,15 +7237,15 @@
         </is>
       </c>
       <c r="AJ43" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A43,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A43,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK43" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A43,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A43,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL43" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A43,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A43,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM43" s="9" t="n">
@@ -7386,15 +7398,15 @@
         </is>
       </c>
       <c r="AJ44" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A44,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A44,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK44" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A44,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A44,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL44" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A44,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A44,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM44" s="9" t="n"/>
@@ -7537,15 +7549,15 @@
       <c r="AH45" s="9" t="n"/>
       <c r="AI45" s="9" t="n"/>
       <c r="AJ45" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A45,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A45,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK45" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A45,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A45,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL45" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A45,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A45,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM45" s="9" t="n"/>
@@ -7688,15 +7700,15 @@
         </is>
       </c>
       <c r="AJ46" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A46,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A46,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK46" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A46,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A46,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL46" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A46,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A46,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM46" s="9" t="n"/>
@@ -7832,18 +7844,24 @@
         <v>0</v>
       </c>
       <c r="AG47" s="9" t="n"/>
-      <c r="AH47" s="9" t="n"/>
-      <c r="AI47" s="9" t="n"/>
+      <c r="AH47" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI47" s="9" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="AJ47" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A47,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A47,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK47" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A47,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A47,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL47" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A47,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A47,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM47" s="9" t="n">
@@ -7984,15 +8002,15 @@
         </is>
       </c>
       <c r="AJ48" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A48,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A48,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK48" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A48,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A48,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL48" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A48,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A48,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM48" s="9" t="n">
@@ -8137,15 +8155,15 @@
       <c r="AH49" s="9" t="n"/>
       <c r="AI49" s="9" t="n"/>
       <c r="AJ49" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A49,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A49,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK49" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A49,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A49,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL49" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A49,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A49,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM49" s="9" t="n">
@@ -8294,15 +8312,15 @@
       <c r="AH50" s="9" t="n"/>
       <c r="AI50" s="9" t="n"/>
       <c r="AJ50" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A50,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A50,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK50" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A50,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A50,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL50" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A50,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A50,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM50" s="9" t="n">
@@ -8449,15 +8467,15 @@
         </is>
       </c>
       <c r="AJ51" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A51,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A51,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK51" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A51,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A51,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL51" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A51,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A51,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM51" s="9" t="n">
@@ -8612,15 +8630,15 @@
         </is>
       </c>
       <c r="AJ52" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A52,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A52,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK52" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A52,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A52,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL52" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A52,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A52,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM52" s="9" t="n">
@@ -8764,18 +8782,24 @@
           <t>1 de 340 posts não carregou; o primeiro post pode ser anterior</t>
         </is>
       </c>
-      <c r="AH53" s="9" t="n"/>
-      <c r="AI53" s="9" t="n"/>
+      <c r="AH53" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI53" s="9" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="AJ53" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A53,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A53,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK53" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A53,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A53,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL53" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A53,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A53,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM53" s="9" t="n">
@@ -8920,15 +8944,15 @@
       <c r="AH54" s="9" t="n"/>
       <c r="AI54" s="9" t="n"/>
       <c r="AJ54" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A54,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A54,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK54" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A54,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A54,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL54" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A54,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A54,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM54" s="9" t="n"/>
@@ -9065,15 +9089,15 @@
         </is>
       </c>
       <c r="AJ55" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$34,MATCH($A55,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A55,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AK55" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$34,MATCH($A55,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A55,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AL55" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$34,MATCH($A55,cesta!$A$2:$A$34,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A55,cesta!$A$2:$A$37,0)),"")</f>
         <v/>
       </c>
       <c r="AM55" s="9" t="n"/>
@@ -9734,7 +9758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W34"/>
+  <dimension ref="A1:W37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10860,12 +10884,12 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>ChIJc3F7ka83J5URQZ1XTl-_iak</t>
+          <t>ChIJawIVeV0JM0oR5BtnD_poQeA</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Chef on Play</t>
+          <t>CCG Floripa</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -10874,7 +10898,7 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
@@ -10890,23 +10914,17 @@
       <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n">
-        <v>21.9</v>
+        <v>36</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>25.9</v>
+        <v>36</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>28.9</v>
+        <v>51</v>
       </c>
       <c r="O14" s="12">
         <f>IF(OR(I14="",L14=""),"",F14+I14+L14)</f>
@@ -10921,29 +10939,29 @@
         <v/>
       </c>
       <c r="R14" s="12" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="S14" s="12" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="S14" s="12" t="n">
+        <v>54</v>
+      </c>
       <c r="T14" s="12" t="n"/>
-      <c r="U14" s="12" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="U14" s="12" t="n"/>
       <c r="V14" s="12" t="n"/>
       <c r="W14" s="9" t="inlineStr">
         <is>
-          <t>2022-12, 2024-01, 2025-04</t>
+          <t>2023-07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>ChIJJz8-gcY3J5URYdZrEXdHaAk</t>
+          <t>ChIJc3F7ka83J5URQZ1XTl-_iak</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Cineplay- Restaurante e Jogos</t>
+          <t>Chef on Play</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -10952,7 +10970,7 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
@@ -10969,22 +10987,22 @@
         <v>0</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>17.9</v>
+        <v>6.8</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>20.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L15" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="M15" s="12" t="n">
         <v>25.9</v>
       </c>
-      <c r="M15" s="12" t="n">
-        <v>30.9</v>
-      </c>
       <c r="N15" s="12" t="n">
-        <v>46.77</v>
+        <v>28.9</v>
       </c>
       <c r="O15" s="12">
         <f>IF(OR(I15="",L15=""),"",F15+I15+L15)</f>
@@ -10999,44 +11017,38 @@
         <v/>
       </c>
       <c r="R15" s="12" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="S15" s="12" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="T15" s="12" t="n">
-        <v>17</v>
-      </c>
+        <v>25.9</v>
+      </c>
+      <c r="S15" s="12" t="n"/>
+      <c r="T15" s="12" t="n"/>
       <c r="U15" s="12" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="V15" s="12" t="n">
-        <v>20.9</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="V15" s="12" t="n"/>
       <c r="W15" s="9" t="inlineStr">
         <is>
-          <t>2022-10, 2023-05, 2023-09, 2024-06</t>
+          <t>2022-12, 2024-01, 2025-04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>ChIJ0yXbI35IxwcR0_jLi-uINUU</t>
+          <t>ChIJJz8-gcY3J5URYdZrEXdHaAk</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Balboa's Hobby Games</t>
+          <t>Cineplay- Restaurante e Jogos</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Florianópolis</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
@@ -11053,22 +11065,22 @@
         <v>0</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>8</v>
+        <v>17.9</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>15</v>
+        <v>20.9</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>28</v>
+        <v>25.9</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>30</v>
+        <v>30.9</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>30</v>
+        <v>46.77</v>
       </c>
       <c r="O16" s="12">
         <f>IF(OR(I16="",L16=""),"",F16+I16+L16)</f>
@@ -11083,44 +11095,44 @@
         <v/>
       </c>
       <c r="R16" s="12" t="n">
-        <v>29.5</v>
+        <v>29.9</v>
       </c>
       <c r="S16" s="12" t="n">
-        <v>26.5</v>
+        <v>29.2</v>
       </c>
       <c r="T16" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="U16" s="12" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>15</v>
+        <v>20.9</v>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2022-10, 2023-05, 2023-09, 2024-06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>ChIJHSDPTgF5GZURKmSqKITyoGM</t>
+          <t>ChIJ0yXbI35IxwcR0_jLi-uINUU</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Arcadea Gaming Pub</t>
+          <t>Balboa's Hobby Games</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Porto Alegre</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
@@ -11137,22 +11149,22 @@
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>17.75</v>
+        <v>7</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="O17" s="12">
         <f>IF(OR(I17="",L17=""),"",F17+I17+L17)</f>
@@ -11167,35 +11179,35 @@
         <v/>
       </c>
       <c r="R17" s="12" t="n">
-        <v>45</v>
+        <v>29.5</v>
       </c>
       <c r="S17" s="12" t="n">
-        <v>28</v>
+        <v>26.5</v>
       </c>
       <c r="T17" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="U17" s="12" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>ChIJ41pgHNFDGZURC7yTegyn7nU</t>
+          <t>ChIJHSDPTgF5GZURKmSqKITyoGM</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Toca do Rato - Pizzaria e Jogos de Tabuleiro</t>
+          <t>Arcadea Gaming Pub</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -11204,39 +11216,39 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="J18" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>7.5</v>
-      </c>
       <c r="K18" s="12" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>57.17</v>
+        <v>35</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>64.45</v>
+        <v>40</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>71.5</v>
+        <v>45</v>
       </c>
       <c r="O18" s="12">
         <f>IF(OR(I18="",L18=""),"",F18+I18+L18)</f>
@@ -11250,33 +11262,41 @@
         <f>IF(OR(K18="",N18=""),"",H18+K18+N18)</f>
         <v/>
       </c>
-      <c r="R18" s="12" t="n"/>
-      <c r="S18" s="12" t="n"/>
-      <c r="T18" s="12" t="n"/>
+      <c r="R18" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="S18" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="T18" s="12" t="n">
+        <v>19</v>
+      </c>
       <c r="U18" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V18" s="12" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="V18" s="12" t="n">
+        <v>29</v>
+      </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2025-03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>ChIJRUjwU66WoGgRzc9yJU7jkwM</t>
+          <t>ChIJ41pgHNFDGZURC7yTegyn7nU</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Nala Land - Bar de Jogos de Tabuleiro em Recife</t>
+          <t>Toca do Rato - Pizzaria e Jogos de Tabuleiro</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Recife</t>
+          <t>Porto Alegre</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
@@ -11297,22 +11317,22 @@
         <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>18</v>
+        <v>57.17</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>22</v>
+        <v>64.45</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>25</v>
+        <v>71.5</v>
       </c>
       <c r="O19" s="12">
         <f>IF(OR(I19="",L19=""),"",F19+I19+L19)</f>
@@ -11326,16 +11346,12 @@
         <f>IF(OR(K19="",N19=""),"",H19+K19+N19)</f>
         <v/>
       </c>
-      <c r="R19" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="S19" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="T19" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="U19" s="12" t="n"/>
+      <c r="R19" s="12" t="n"/>
+      <c r="S19" s="12" t="n"/>
+      <c r="T19" s="12" t="n"/>
+      <c r="U19" s="12" t="n">
+        <v>7.5</v>
+      </c>
       <c r="V19" s="12" t="n"/>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -11346,21 +11362,21 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>ChIJ90Gs_9rVmwAReA7MnIyPLTE</t>
+          <t>ChIJRUjwU66WoGgRzc9yJU7jkwM</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Luderia Carioca</t>
+          <t>Nala Land - Bar de Jogos de Tabuleiro em Recife</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Recife</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
@@ -11377,22 +11393,22 @@
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="O20" s="12">
         <f>IF(OR(I20="",L20=""),"",F20+I20+L20)</f>
@@ -11407,17 +11423,15 @@
         <v/>
       </c>
       <c r="R20" s="12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S20" s="12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="T20" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="U20" s="12" t="n">
-        <v>9</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="U20" s="12" t="n"/>
       <c r="V20" s="12" t="n"/>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -11428,21 +11442,21 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>ChIJoTlvBfMbFgcRHvuCKHBQrXQ</t>
+          <t>ChIJ90Gs_9rVmwAReA7MnIyPLTE</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>São Jogue - Bela Vista</t>
+          <t>Luderia Carioca</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
@@ -11459,19 +11473,19 @@
         <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J21" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="K21" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>24.25</v>
+        <v>26</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>37.5</v>
@@ -11489,76 +11503,74 @@
         <v/>
       </c>
       <c r="R21" s="12" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="S21" s="12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="T21" s="12" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="U21" s="12" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V21" s="12" t="n">
-        <v>28</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="V21" s="12" t="n"/>
       <c r="W21" s="9" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>ChIJYTHwWgBbzpQRFenbJdM5cxU</t>
+          <t>ChIJoTlvBfMbFgcRHvuCKHBQrXQ</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Arena BG | Jogos de Tabuleiro | Hamburgueria</t>
+          <t>São Jogue - Bela Vista</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Salvador</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>não</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>38</v>
+        <v>24.25</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>45</v>
+        <v>32.5</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>58</v>
+        <v>37.5</v>
       </c>
       <c r="O22" s="12">
         <f>IF(OR(I22="",L22=""),"",F22+I22+L22)</f>
@@ -11573,35 +11585,35 @@
         <v/>
       </c>
       <c r="R22" s="12" t="n">
-        <v>52.5</v>
+        <v>45</v>
       </c>
       <c r="S22" s="12" t="n">
-        <v>28.5</v>
+        <v>35</v>
       </c>
       <c r="T22" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U22" s="12" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2026-10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>ChIJKeHwNv5ZzpQRlmzx9rCTWdM</t>
+          <t>ChIJYTHwWgBbzpQRFenbJdM5cxU</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Bodogami Restaurante e Cafeteria</t>
+          <t>Arena BG | Jogos de Tabuleiro | Hamburgueria</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -11610,39 +11622,39 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>27.5</v>
+        <v>20</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>48.5</v>
+        <v>58</v>
       </c>
       <c r="O23" s="12">
         <f>IF(OR(I23="",L23=""),"",F23+I23+L23)</f>
@@ -11657,35 +11669,35 @@
         <v/>
       </c>
       <c r="R23" s="12" t="n">
-        <v>49.5</v>
+        <v>52.5</v>
       </c>
       <c r="S23" s="12" t="n">
-        <v>39</v>
+        <v>28.5</v>
       </c>
       <c r="T23" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="U23" s="12" t="n">
         <v>8</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>36.5</v>
+        <v>25</v>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>ChIJrT_EWwBZzpQRGAZzptZbtsY</t>
+          <t>ChIJKeHwNv5ZzpQRlmzx9rCTWdM</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Cartola Luderia Bar</t>
+          <t>Bodogami Restaurante e Cafeteria</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -11694,7 +11706,7 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
@@ -11711,22 +11723,22 @@
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>29.75</v>
+        <v>25</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>40</v>
+        <v>48.5</v>
       </c>
       <c r="O24" s="12">
         <f>IF(OR(I24="",L24=""),"",F24+I24+L24)</f>
@@ -11740,30 +11752,36 @@
         <f>IF(OR(K24="",N24=""),"",H24+K24+N24)</f>
         <v/>
       </c>
-      <c r="R24" s="12" t="n"/>
+      <c r="R24" s="12" t="n">
+        <v>49.5</v>
+      </c>
       <c r="S24" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="T24" s="12" t="n"/>
-      <c r="U24" s="12" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="T24" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="U24" s="12" t="n">
+        <v>8</v>
+      </c>
       <c r="V24" s="12" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2025-03-19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>ChIJbZRHQPRfzpQRz97-ZOg0yXA</t>
+          <t>ChIJrT_EWwBZzpQRGAZzptZbtsY</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Castelos Bar &amp; Boardgames</t>
+          <t>Cartola Luderia Bar</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -11772,7 +11790,7 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
@@ -11789,22 +11807,22 @@
         <v>0</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>16.42</v>
+        <v>29</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>28.4</v>
+        <v>36</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>39.15</v>
+        <v>29.75</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>43.4</v>
+        <v>39</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>45.65</v>
+        <v>40</v>
       </c>
       <c r="O25" s="12">
         <f>IF(OR(I25="",L25=""),"",F25+I25+L25)</f>
@@ -11818,20 +11836,14 @@
         <f>IF(OR(K25="",N25=""),"",H25+K25+N25)</f>
         <v/>
       </c>
-      <c r="R25" s="12" t="n">
-        <v>43.9</v>
-      </c>
+      <c r="R25" s="12" t="n"/>
       <c r="S25" s="12" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="T25" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="U25" s="12" t="n">
-        <v>9</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="T25" s="12" t="n"/>
+      <c r="U25" s="12" t="n"/>
       <c r="V25" s="12" t="n">
-        <v>37.9</v>
+        <v>36</v>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -11842,12 +11854,12 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>ChIJF9j3OCRbzpQRkk74_QtOk_0</t>
+          <t>ChIJbZRHQPRfzpQRz97-ZOg0yXA</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Coletivo Geek</t>
+          <t>Castelos Bar &amp; Boardgames</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -11856,7 +11868,7 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
@@ -11873,22 +11885,22 @@
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>20.25</v>
+        <v>16.42</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>30</v>
+        <v>37.9</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>27.5</v>
+        <v>39.15</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>32</v>
+        <v>43.4</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>39</v>
+        <v>45.65</v>
       </c>
       <c r="O26" s="12">
         <f>IF(OR(I26="",L26=""),"",F26+I26+L26)</f>
@@ -11903,35 +11915,35 @@
         <v/>
       </c>
       <c r="R26" s="12" t="n">
-        <v>28</v>
+        <v>43.9</v>
       </c>
       <c r="S26" s="12" t="n">
-        <v>33</v>
+        <v>39.9</v>
       </c>
       <c r="T26" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="U26" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>30</v>
+        <v>37.9</v>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>ChIJ7_DDAlH1zpQRJVJ0UHnItH8</t>
+          <t>ChIJF9j3OCRbzpQRkk74_QtOk_0</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Covil Game Bar</t>
+          <t>Coletivo Geek</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -11940,7 +11952,7 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
@@ -11957,22 +11969,22 @@
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>14</v>
+        <v>20.25</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O27" s="12">
         <f>IF(OR(I27="",L27=""),"",F27+I27+L27)</f>
@@ -11987,35 +11999,35 @@
         <v/>
       </c>
       <c r="R27" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S27" s="12" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="T27" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="U27" s="12" t="n">
         <v>8</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>21.5</v>
+        <v>30</v>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>ChIJiZJ_DnIDz5QRaVafFCXGkUE</t>
+          <t>ChIJ7_DDAlH1zpQRJVJ0UHnItH8</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Dungeon Games Store</t>
+          <t>Covil Game Bar</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -12024,7 +12036,7 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
@@ -12041,22 +12053,22 @@
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>25.75</v>
+        <v>29</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>32.5</v>
+        <v>38</v>
       </c>
       <c r="O28" s="12">
         <f>IF(OR(I28="",L28=""),"",F28+I28+L28)</f>
@@ -12071,35 +12083,35 @@
         <v/>
       </c>
       <c r="R28" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S28" s="12" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T28" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="U28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>28</v>
+        <v>21.5</v>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2025-07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>ChIJZz29dnVXzpQRvRh7_YKyUN4</t>
+          <t>ChIJiZJ_DnIDz5QRaVafFCXGkUE</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Encounter | Jogos de Tabuleiro | Board Games</t>
+          <t>Dungeon Games Store</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -12108,7 +12120,7 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
@@ -12125,22 +12137,22 @@
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>27.9</v>
+        <v>10</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>27.9</v>
+        <v>14</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>27.9</v>
+        <v>20</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>34.9</v>
+        <v>25.75</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>39.9</v>
+        <v>30</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>48.9</v>
+        <v>32.5</v>
       </c>
       <c r="O29" s="12">
         <f>IF(OR(I29="",L29=""),"",F29+I29+L29)</f>
@@ -12155,29 +12167,35 @@
         <v/>
       </c>
       <c r="R29" s="12" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="S29" s="12" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="T29" s="12" t="n"/>
-      <c r="U29" s="12" t="n"/>
-      <c r="V29" s="12" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="T29" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U29" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="V29" s="12" t="n">
+        <v>28</v>
+      </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>ChIJa3UsDhRczpQRPPSuDl6acO8</t>
+          <t>ChIJZz29dnVXzpQRvRh7_YKyUN4</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Flow Games - Burgers, Cards &amp; Comunidade</t>
+          <t>Encounter | Jogos de Tabuleiro | Board Games</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -12186,7 +12204,7 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
@@ -12203,22 +12221,22 @@
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>6</v>
+        <v>27.9</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>6</v>
+        <v>27.9</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>7</v>
+        <v>27.9</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>11</v>
+        <v>34.9</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>14</v>
+        <v>39.9</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>34.9</v>
+        <v>48.9</v>
       </c>
       <c r="O30" s="12">
         <f>IF(OR(I30="",L30=""),"",F30+I30+L30)</f>
@@ -12233,33 +12251,29 @@
         <v/>
       </c>
       <c r="R30" s="12" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="S30" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="U30" s="12" t="n">
-        <v>6</v>
-      </c>
+        <v>24.9</v>
+      </c>
+      <c r="T30" s="12" t="n"/>
+      <c r="U30" s="12" t="n"/>
       <c r="V30" s="12" t="n"/>
       <c r="W30" s="9" t="inlineStr">
         <is>
-          <t>2022-09, 2025-08</t>
+          <t>2025-06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>ChIJTaG5ALpZzpQRUDErQ-RkfTs</t>
+          <t>ChIJa3UsDhRczpQRPPSuDl6acO8</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Ludus Luderia</t>
+          <t>Flow Games - Burgers, Cards &amp; Comunidade</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -12268,11 +12282,11 @@
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>não</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
@@ -12285,22 +12299,22 @@
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>56.5</v>
+        <v>34.9</v>
       </c>
       <c r="O31" s="12">
         <f>IF(OR(I31="",L31=""),"",F31+I31+L31)</f>
@@ -12315,35 +12329,33 @@
         <v/>
       </c>
       <c r="R31" s="12" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="S31" s="12" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="T31" s="12" t="n">
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="U31" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="V31" s="12" t="n">
-        <v>36</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="V31" s="12" t="n"/>
       <c r="W31" s="9" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2022-09, 2025-08</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>ChIJkWsGmd1czpQRGLydxc29vbw</t>
+          <t>ChIJn7uU0RNbzpQRI4GI9KHOo_s</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Place Games</t>
+          <t>Jogasampa</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -12352,7 +12364,7 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
@@ -12369,23 +12381,17 @@
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>7.18</v>
+        <v>6</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="N32" s="12" t="n">
-        <v>39</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
       <c r="O32" s="12">
         <f>IF(OR(I32="",L32=""),"",F32+I32+L32)</f>
         <v/>
@@ -12398,34 +12404,28 @@
         <f>IF(OR(K32="",N32=""),"",H32+K32+N32)</f>
         <v/>
       </c>
-      <c r="R32" s="12" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="S32" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="T32" s="12" t="n">
-        <v>13</v>
-      </c>
+      <c r="R32" s="12" t="n"/>
+      <c r="S32" s="12" t="n"/>
+      <c r="T32" s="12" t="n"/>
       <c r="U32" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="V32" s="12" t="n"/>
       <c r="W32" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2023-10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>ChIJNcHw7jNYzpQRKRHPOrb4jEw</t>
+          <t>ChIJTaG5ALpZzpQRUDErQ-RkfTs</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Play Easy</t>
+          <t>Ludus Luderia</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -12434,11 +12434,11 @@
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
@@ -12451,22 +12451,22 @@
         <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>9.5</v>
+        <v>36</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>25</v>
+        <v>56.5</v>
       </c>
       <c r="O33" s="12">
         <f>IF(OR(I33="",L33=""),"",F33+I33+L33)</f>
@@ -12480,41 +12480,45 @@
         <f>IF(OR(K33="",N33=""),"",H33+K33+N33)</f>
         <v/>
       </c>
-      <c r="R33" s="12" t="n"/>
+      <c r="R33" s="12" t="n">
+        <v>42</v>
+      </c>
       <c r="S33" s="12" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="T33" s="12" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="U33" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V33" s="12" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="V33" s="12" t="n">
+        <v>36</v>
+      </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2023-06-07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>ChIJfyav9YI9uAARjwbBqcRm2_k</t>
+          <t>ChIJkWsGmd1czpQRGLydxc29vbw</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Café Geek Cafeteria e Ludoteca</t>
+          <t>Place Games</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
@@ -12531,22 +12535,22 @@
         <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>7.75</v>
+        <v>7.18</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>15.25</v>
+        <v>39</v>
       </c>
       <c r="O34" s="12">
         <f>IF(OR(I34="",L34=""),"",F34+I34+L34)</f>
@@ -12560,15 +12564,17 @@
         <f>IF(OR(K34="",N34=""),"",H34+K34+N34)</f>
         <v/>
       </c>
-      <c r="R34" s="12" t="n"/>
+      <c r="R34" s="12" t="n">
+        <v>38.9</v>
+      </c>
       <c r="S34" s="12" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="T34" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U34" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V34" s="12" t="n"/>
       <c r="W34" s="9" t="inlineStr">
@@ -12577,8 +12583,240 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>ChIJNcHw7jNYzpQRKRHPOrb4jEw</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Play Easy</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="N35" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="O35" s="12">
+        <f>IF(OR(I35="",L35=""),"",F35+I35+L35)</f>
+        <v/>
+      </c>
+      <c r="P35" s="12">
+        <f>IF(OR(J35="",M35=""),"",G35+J35+M35)</f>
+        <v/>
+      </c>
+      <c r="Q35" s="12">
+        <f>IF(OR(K35="",N35=""),"",H35+K35+N35)</f>
+        <v/>
+      </c>
+      <c r="R35" s="12" t="n"/>
+      <c r="S35" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="T35" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="U35" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V35" s="12" t="n"/>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>sem data</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>ChIJsU5BAwBRzpQRAgLVvqg68os</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Tubaleria</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="N36" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="O36" s="12">
+        <f>IF(OR(I36="",L36=""),"",F36+I36+L36)</f>
+        <v/>
+      </c>
+      <c r="P36" s="12">
+        <f>IF(OR(J36="",M36=""),"",G36+J36+M36)</f>
+        <v/>
+      </c>
+      <c r="Q36" s="12">
+        <f>IF(OR(K36="",N36=""),"",H36+K36+N36)</f>
+        <v/>
+      </c>
+      <c r="R36" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="S36" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="T36" s="12" t="n"/>
+      <c r="U36" s="12" t="n"/>
+      <c r="V36" s="12" t="n"/>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>2025-12, 2026-01, 2026-03, 2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>ChIJfyav9YI9uAARjwbBqcRm2_k</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Café Geek Cafeteria e Ludoteca</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N37" s="12" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="O37" s="12">
+        <f>IF(OR(I37="",L37=""),"",F37+I37+L37)</f>
+        <v/>
+      </c>
+      <c r="P37" s="12">
+        <f>IF(OR(J37="",M37=""),"",G37+J37+M37)</f>
+        <v/>
+      </c>
+      <c r="Q37" s="12">
+        <f>IF(OR(K37="",N37=""),"",H37+K37+N37)</f>
+        <v/>
+      </c>
+      <c r="R37" s="12" t="n"/>
+      <c r="S37" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="T37" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U37" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="V37" s="12" t="n"/>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>sem data</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W34"/>
+  <autoFilter ref="A1:W37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/B1_resumo_estabelecimentos.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/B1_resumo_estabelecimentos.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'estabelecimentos'!$A$1:$AP$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'por_capital'!$A$1:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'cesta'!$A$1:$W$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'cesta'!$A$1:$W$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'dicionario'!$A$1:$E$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -862,12 +862,8 @@
       <c r="V2" s="9" t="n">
         <v>307</v>
       </c>
-      <c r="W2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="W2" s="9" t="n"/>
+      <c r="X2" s="9" t="n"/>
       <c r="Y2" s="9" t="n">
         <v>723</v>
       </c>
@@ -904,19 +900,19 @@
       </c>
       <c r="AI2" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ2" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A2,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A2,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK2" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A2,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A2,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL2" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A2,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A2,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM2" s="9" t="n">
@@ -1016,15 +1012,9 @@
       <c r="U3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="9" t="n">
-        <v>1142</v>
-      </c>
-      <c r="W3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="V3" s="9" t="n"/>
+      <c r="W3" s="9" t="n"/>
+      <c r="X3" s="9" t="n"/>
       <c r="Y3" s="9" t="n">
         <v>105</v>
       </c>
@@ -1063,15 +1053,15 @@
         </is>
       </c>
       <c r="AJ3" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A3,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A3,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK3" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A3,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A3,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL3" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A3,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A3,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM3" s="9" t="n">
@@ -1175,12 +1165,8 @@
       <c r="U4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>1201</v>
-      </c>
-      <c r="W4" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="V4" s="9" t="n"/>
+      <c r="W4" s="9" t="n"/>
       <c r="X4" s="9" t="n"/>
       <c r="Y4" s="9" t="n">
         <v>754</v>
@@ -1211,18 +1197,24 @@
         <v>10</v>
       </c>
       <c r="AG4" s="9" t="n"/>
-      <c r="AH4" s="9" t="n"/>
-      <c r="AI4" s="9" t="n"/>
+      <c r="AH4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="AJ4" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A4,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A4,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK4" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A4,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A4,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL4" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A4,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A4,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM4" s="9" t="n"/>
@@ -1320,15 +1312,9 @@
       <c r="U5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="9" t="n">
-        <v>4984</v>
-      </c>
-      <c r="W5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="9" t="n"/>
+      <c r="X5" s="9" t="n"/>
       <c r="Y5" s="9" t="n">
         <v>137</v>
       </c>
@@ -1363,15 +1349,15 @@
         </is>
       </c>
       <c r="AJ5" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A5,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A5,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK5" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A5,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A5,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL5" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A5,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A5,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM5" s="9" t="n">
@@ -1475,15 +1461,9 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>3205</v>
-      </c>
-      <c r="W6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="V6" s="9" t="n"/>
+      <c r="W6" s="9" t="n"/>
+      <c r="X6" s="9" t="n"/>
       <c r="Y6" s="9" t="n">
         <v>391</v>
       </c>
@@ -1517,18 +1497,24 @@
           <t>perfil da editora; a triagem aponta @ludocafebh</t>
         </is>
       </c>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="9" t="n"/>
+      <c r="AH6" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI6" s="9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="AJ6" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A6,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A6,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK6" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A6,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A6,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL6" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A6,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A6,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM6" s="9" t="n">
@@ -1636,9 +1622,7 @@
       <c r="U7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="9" t="n">
-        <v>2556</v>
-      </c>
+      <c r="V7" s="9" t="n"/>
       <c r="W7" s="9" t="n"/>
       <c r="X7" s="9" t="n"/>
       <c r="Y7" s="9" t="n">
@@ -1679,15 +1663,15 @@
         </is>
       </c>
       <c r="AJ7" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A7,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A7,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK7" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A7,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A7,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL7" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A7,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A7,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
@@ -1792,12 +1776,8 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n"/>
-      <c r="W8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="W8" s="9" t="n"/>
+      <c r="X8" s="9" t="n"/>
       <c r="Y8" s="9" t="n">
         <v>52</v>
       </c>
@@ -1828,7 +1808,7 @@
       </c>
       <c r="AG8" s="9" t="n"/>
       <c r="AH8" s="9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AI8" s="9" t="inlineStr">
         <is>
@@ -1836,15 +1816,15 @@
         </is>
       </c>
       <c r="AJ8" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A8,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A8,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK8" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A8,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A8,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL8" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A8,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A8,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM8" s="9" t="n">
@@ -1959,12 +1939,8 @@
       <c r="V9" s="9" t="n">
         <v>768</v>
       </c>
-      <c r="W9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="W9" s="9" t="n"/>
+      <c r="X9" s="9" t="n"/>
       <c r="Y9" s="9" t="n">
         <v>305</v>
       </c>
@@ -1999,19 +1975,19 @@
       </c>
       <c r="AI9" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ9" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A9,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A9,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK9" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A9,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A9,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL9" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A9,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A9,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM9" s="9" t="n"/>
@@ -2109,9 +2085,7 @@
       <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="9" t="n">
-        <v>3099</v>
-      </c>
+      <c r="V10" s="9" t="n"/>
       <c r="W10" s="9" t="n"/>
       <c r="X10" s="9" t="n"/>
       <c r="Y10" s="9" t="n">
@@ -2146,15 +2120,15 @@
       <c r="AH10" s="9" t="n"/>
       <c r="AI10" s="9" t="n"/>
       <c r="AJ10" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A10,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A10,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK10" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A10,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A10,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL10" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A10,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A10,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM10" s="9" t="n"/>
@@ -2259,15 +2233,9 @@
       <c r="V11" s="9" t="n">
         <v>702</v>
       </c>
-      <c r="W11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="9" t="n">
-        <v>1505</v>
-      </c>
+      <c r="W11" s="9" t="n"/>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
       <c r="Z11" s="9" t="inlineStr">
         <is>
           <t>insidegamestore</t>
@@ -2299,19 +2267,19 @@
       </c>
       <c r="AI11" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ11" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A11,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A11,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK11" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A11,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A11,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL11" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A11,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A11,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM11" s="9" t="n"/>
@@ -2460,15 +2428,15 @@
         </is>
       </c>
       <c r="AJ12" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A12,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A12,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK12" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A12,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A12,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL12" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A12,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A12,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM12" s="9" t="n">
@@ -2579,12 +2547,8 @@
       <c r="V13" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="W13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="W13" s="9" t="n"/>
+      <c r="X13" s="9" t="n"/>
       <c r="Y13" s="9" t="n">
         <v>747</v>
       </c>
@@ -2623,15 +2587,15 @@
         </is>
       </c>
       <c r="AJ13" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A13,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A13,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK13" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A13,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A13,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL13" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A13,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A13,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM13" s="9" t="n">
@@ -2739,15 +2703,9 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>6361</v>
-      </c>
-      <c r="W14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="V14" s="9" t="n"/>
+      <c r="W14" s="9" t="n"/>
+      <c r="X14" s="9" t="n"/>
       <c r="Y14" s="9" t="n">
         <v>162</v>
       </c>
@@ -2782,19 +2740,19 @@
       </c>
       <c r="AI14" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ14" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A14,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A14,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK14" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A14,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A14,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL14" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A14,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A14,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM14" s="9" t="n"/>
@@ -2893,9 +2851,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n"/>
-      <c r="W15" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="W15" s="9" t="n"/>
       <c r="X15" s="9" t="n"/>
       <c r="Y15" s="9" t="n">
         <v>770</v>
@@ -2927,23 +2883,23 @@
       </c>
       <c r="AG15" s="9" t="n"/>
       <c r="AH15" s="9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI15" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ15" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A15,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A15,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK15" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A15,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A15,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL15" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A15,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A15,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM15" s="9" t="n">
@@ -3052,15 +3008,9 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n"/>
-      <c r="W16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="9" t="n">
-        <v>1175</v>
-      </c>
+      <c r="W16" s="9" t="n"/>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
       <c r="Z16" s="9" t="inlineStr">
         <is>
           <t>boardzgamepub</t>
@@ -3088,23 +3038,23 @@
       </c>
       <c r="AG16" s="9" t="n"/>
       <c r="AH16" s="9" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="AI16" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ16" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A16,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A16,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK16" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A16,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A16,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL16" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A16,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A16,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM16" s="9" t="n"/>
@@ -3207,15 +3157,9 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n"/>
-      <c r="W17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="9" t="n">
-        <v>1152</v>
-      </c>
+      <c r="W17" s="9" t="n"/>
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="9" t="n"/>
       <c r="Z17" s="9" t="inlineStr">
         <is>
           <t>joyjoycafe</t>
@@ -3242,18 +3186,24 @@
         <v>114</v>
       </c>
       <c r="AG17" s="9" t="n"/>
-      <c r="AH17" s="9" t="n"/>
-      <c r="AI17" s="9" t="n"/>
+      <c r="AH17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI17" s="9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="AJ17" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A17,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A17,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK17" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A17,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A17,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL17" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A17,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A17,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM17" s="9" t="n">
@@ -3388,15 +3338,15 @@
       <c r="AH18" s="9" t="n"/>
       <c r="AI18" s="9" t="n"/>
       <c r="AJ18" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A18,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A18,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK18" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A18,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A18,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL18" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A18,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A18,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM18" s="9" t="n"/>
@@ -3533,15 +3483,15 @@
       <c r="AH19" s="9" t="n"/>
       <c r="AI19" s="9" t="n"/>
       <c r="AJ19" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A19,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A19,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK19" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A19,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A19,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL19" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A19,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A19,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM19" s="9" t="n"/>
@@ -3648,12 +3598,8 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n"/>
-      <c r="W20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="W20" s="9" t="n"/>
+      <c r="X20" s="9" t="n"/>
       <c r="Y20" s="9" t="n">
         <v>590</v>
       </c>
@@ -3686,15 +3632,15 @@
       <c r="AH20" s="9" t="n"/>
       <c r="AI20" s="9" t="n"/>
       <c r="AJ20" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A20,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A20,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK20" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A20,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A20,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL20" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A20,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A20,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM20" s="9" t="n"/>
@@ -3793,12 +3739,8 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n"/>
-      <c r="W21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="9" t="n"/>
       <c r="Y21" s="9" t="n">
         <v>294</v>
       </c>
@@ -3829,23 +3771,23 @@
       </c>
       <c r="AG21" s="9" t="n"/>
       <c r="AH21" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI21" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ21" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A21,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A21,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK21" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A21,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A21,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL21" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A21,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A21,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM21" s="9" t="n"/>
@@ -3952,9 +3894,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n"/>
-      <c r="W22" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="W22" s="9" t="n"/>
       <c r="X22" s="9" t="n"/>
       <c r="Y22" s="9" t="n">
         <v>834</v>
@@ -3986,23 +3926,23 @@
       </c>
       <c r="AG22" s="9" t="n"/>
       <c r="AH22" s="9" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AI22" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ22" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A22,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A22,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK22" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A22,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A22,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL22" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A22,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A22,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM22" s="9" t="n">
@@ -4115,15 +4055,9 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n"/>
-      <c r="W23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="9" t="n">
-        <v>1681</v>
-      </c>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="9" t="n"/>
+      <c r="Y23" s="9" t="n"/>
       <c r="Z23" s="9" t="inlineStr">
         <is>
           <t>cineplay_sc</t>
@@ -4151,23 +4085,23 @@
       </c>
       <c r="AG23" s="9" t="n"/>
       <c r="AH23" s="9" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="AI23" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ23" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A23,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A23,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK23" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A23,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A23,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL23" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A23,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A23,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM23" s="9" t="n"/>
@@ -4265,9 +4199,7 @@
       <c r="U24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>3702</v>
-      </c>
+      <c r="V24" s="9" t="n"/>
       <c r="W24" s="9" t="n"/>
       <c r="X24" s="9" t="n"/>
       <c r="Y24" s="9" t="n">
@@ -4304,19 +4236,19 @@
       </c>
       <c r="AI24" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ24" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A24,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A24,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK24" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A24,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A24,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL24" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A24,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A24,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM24" s="9" t="n">
@@ -4469,15 +4401,15 @@
       <c r="AH25" s="9" t="n"/>
       <c r="AI25" s="9" t="n"/>
       <c r="AJ25" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A25,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A25,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK25" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A25,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A25,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL25" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A25,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A25,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM25" s="9" t="n"/>
@@ -4584,12 +4516,8 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n"/>
-      <c r="W26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X26" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="W26" s="9" t="n"/>
+      <c r="X26" s="9" t="n"/>
       <c r="Y26" s="9" t="n">
         <v>5</v>
       </c>
@@ -4622,15 +4550,15 @@
       <c r="AH26" s="9" t="n"/>
       <c r="AI26" s="9" t="n"/>
       <c r="AJ26" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A26,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A26,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK26" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A26,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A26,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL26" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A26,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A26,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM26" s="9" t="n">
@@ -4742,12 +4670,8 @@
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="9" t="n">
-        <v>1300</v>
-      </c>
-      <c r="W27" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="V27" s="9" t="n"/>
+      <c r="W27" s="9" t="n"/>
       <c r="X27" s="9" t="n"/>
       <c r="Y27" s="9" t="n">
         <v>591</v>
@@ -4779,23 +4703,23 @@
       </c>
       <c r="AG27" s="9" t="n"/>
       <c r="AH27" s="9" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI27" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ27" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A27,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A27,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK27" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A27,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A27,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL27" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A27,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A27,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM27" s="9" t="n"/>
@@ -4897,12 +4821,8 @@
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>15504</v>
-      </c>
-      <c r="W28" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="V28" s="9" t="n"/>
+      <c r="W28" s="9" t="n"/>
       <c r="X28" s="9" t="n"/>
       <c r="Y28" s="9" t="n">
         <v>583</v>
@@ -4934,19 +4854,19 @@
       </c>
       <c r="AI28" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ28" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A28,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A28,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK28" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A28,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A28,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL28" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A28,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A28,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM28" s="9" t="n">
@@ -5042,18 +4962,10 @@
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>5144</v>
-      </c>
-      <c r="W29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="9" t="n">
-        <v>1138</v>
-      </c>
+      <c r="V29" s="9" t="n"/>
+      <c r="W29" s="9" t="n"/>
+      <c r="X29" s="9" t="n"/>
+      <c r="Y29" s="9" t="n"/>
       <c r="Z29" s="9" t="inlineStr">
         <is>
           <t>nalaland.jogos</t>
@@ -5085,19 +4997,19 @@
       </c>
       <c r="AI29" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ29" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A29,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A29,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK29" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A29,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A29,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL29" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A29,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A29,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM29" s="9" t="n">
@@ -5235,18 +5147,24 @@
         <v>76</v>
       </c>
       <c r="AG30" s="9" t="n"/>
-      <c r="AH30" s="9" t="n"/>
-      <c r="AI30" s="9" t="n"/>
+      <c r="AH30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI30" s="9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="AJ30" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A30,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A30,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK30" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A30,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A30,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL30" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A30,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A30,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM30" s="9" t="n"/>
@@ -5347,12 +5265,8 @@
       <c r="V31" s="9" t="n">
         <v>302</v>
       </c>
-      <c r="W31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="W31" s="9" t="n"/>
+      <c r="X31" s="9" t="n"/>
       <c r="Y31" s="9" t="n">
         <v>576</v>
       </c>
@@ -5387,19 +5301,19 @@
       </c>
       <c r="AI31" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ31" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A31,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A31,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK31" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A31,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A31,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL31" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A31,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A31,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM31" s="9" t="n">
@@ -5507,15 +5421,9 @@
       <c r="U32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="9" t="n">
-        <v>1216</v>
-      </c>
-      <c r="W32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="V32" s="9" t="n"/>
+      <c r="W32" s="9" t="n"/>
+      <c r="X32" s="9" t="n"/>
       <c r="Y32" s="9" t="n">
         <v>312</v>
       </c>
@@ -5548,15 +5456,15 @@
       <c r="AH32" s="9" t="n"/>
       <c r="AI32" s="9" t="n"/>
       <c r="AJ32" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A32,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A32,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK32" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A32,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A32,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL32" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A32,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A32,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM32" s="9" t="n"/>
@@ -5695,15 +5603,15 @@
       <c r="AH33" s="9" t="n"/>
       <c r="AI33" s="9" t="n"/>
       <c r="AJ33" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A33,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A33,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK33" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A33,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A33,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL33" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A33,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A33,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM33" s="9" t="n"/>
@@ -5805,9 +5713,7 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>7638</v>
-      </c>
+      <c r="V34" s="9" t="n"/>
       <c r="W34" s="9" t="n"/>
       <c r="X34" s="9" t="n"/>
       <c r="Y34" s="9" t="n">
@@ -5835,18 +5741,24 @@
         <v>85</v>
       </c>
       <c r="AG34" s="9" t="n"/>
-      <c r="AH34" s="9" t="n"/>
-      <c r="AI34" s="9" t="n"/>
+      <c r="AH34" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI34" s="9" t="inlineStr">
+        <is>
+          <t>não encontrado</t>
+        </is>
+      </c>
       <c r="AJ34" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A34,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A34,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK34" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A34,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A34,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL34" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A34,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A34,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM34" s="9" t="n">
@@ -5957,12 +5869,8 @@
       <c r="V35" s="9" t="n">
         <v>387</v>
       </c>
-      <c r="W35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X35" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="9" t="n"/>
       <c r="Y35" s="9" t="n">
         <v>118</v>
       </c>
@@ -5997,19 +5905,19 @@
       </c>
       <c r="AI35" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ35" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A35,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A35,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK35" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A35,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A35,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL35" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A35,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A35,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM35" s="9" t="n">
@@ -6116,15 +6024,9 @@
       <c r="V36" s="9" t="n">
         <v>351</v>
       </c>
-      <c r="W36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="9" t="n">
-        <v>1796</v>
-      </c>
+      <c r="W36" s="9" t="n"/>
+      <c r="X36" s="9" t="n"/>
+      <c r="Y36" s="9" t="n"/>
       <c r="Z36" s="9" t="inlineStr">
         <is>
           <t>aarenabg</t>
@@ -6152,7 +6054,7 @@
       </c>
       <c r="AG36" s="9" t="n"/>
       <c r="AH36" s="9" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AI36" s="9" t="inlineStr">
         <is>
@@ -6160,15 +6062,15 @@
         </is>
       </c>
       <c r="AJ36" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A36,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A36,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK36" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A36,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A36,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL36" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A36,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A36,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM36" s="9" t="n">
@@ -6315,23 +6217,23 @@
       </c>
       <c r="AG37" s="9" t="n"/>
       <c r="AH37" s="9" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI37" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ37" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A37,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A37,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK37" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A37,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A37,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL37" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A37,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A37,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM37" s="9" t="n">
@@ -6435,12 +6337,8 @@
       <c r="U38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="9" t="n">
-        <v>10228</v>
-      </c>
-      <c r="W38" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="V38" s="9" t="n"/>
+      <c r="W38" s="9" t="n"/>
       <c r="X38" s="9" t="n"/>
       <c r="Y38" s="9" t="n">
         <v>684</v>
@@ -6470,15 +6368,15 @@
       <c r="AH38" s="9" t="n"/>
       <c r="AI38" s="9" t="n"/>
       <c r="AJ38" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A38,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A38,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK38" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A38,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A38,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL38" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A38,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A38,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM38" s="9" t="n"/>
@@ -6571,9 +6469,7 @@
       <c r="V39" s="9" t="n">
         <v>607</v>
       </c>
-      <c r="W39" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="W39" s="9" t="n"/>
       <c r="X39" s="9" t="n"/>
       <c r="Y39" s="9" t="n">
         <v>907</v>
@@ -6609,19 +6505,19 @@
       </c>
       <c r="AI39" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ39" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A39,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A39,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK39" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A39,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A39,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL39" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A39,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A39,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM39" s="9" t="n"/>
@@ -6722,15 +6618,9 @@
       <c r="V40" s="9" t="n">
         <v>577</v>
       </c>
-      <c r="W40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="9" t="n">
-        <v>1006</v>
-      </c>
+      <c r="W40" s="9" t="n"/>
+      <c r="X40" s="9" t="n"/>
+      <c r="Y40" s="9" t="n"/>
       <c r="Z40" s="9" t="inlineStr">
         <is>
           <t>castelosbareboardgames</t>
@@ -6758,23 +6648,23 @@
       </c>
       <c r="AG40" s="9" t="n"/>
       <c r="AH40" s="9" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AI40" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ40" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A40,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A40,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK40" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A40,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A40,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL40" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A40,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A40,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM40" s="9" t="n">
@@ -6917,23 +6807,23 @@
       </c>
       <c r="AG41" s="9" t="n"/>
       <c r="AH41" s="9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AI41" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ41" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A41,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A41,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK41" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A41,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A41,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL41" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A41,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A41,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM41" s="9" t="n"/>
@@ -7031,15 +6921,9 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>7180</v>
-      </c>
-      <c r="W42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="V42" s="9" t="n"/>
+      <c r="W42" s="9" t="n"/>
+      <c r="X42" s="9" t="n"/>
       <c r="Y42" s="9" t="n">
         <v>424</v>
       </c>
@@ -7074,19 +6958,19 @@
       </c>
       <c r="AI42" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ42" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A42,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A42,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK42" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A42,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A42,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL42" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A42,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A42,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM42" s="9" t="n">
@@ -7190,18 +7074,10 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>16823</v>
-      </c>
-      <c r="W43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="9" t="n">
-        <v>1993</v>
-      </c>
+      <c r="V43" s="9" t="n"/>
+      <c r="W43" s="9" t="n"/>
+      <c r="X43" s="9" t="n"/>
+      <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="inlineStr">
         <is>
           <t>dungeongames.oficial</t>
@@ -7233,19 +7109,19 @@
       </c>
       <c r="AI43" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ43" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A43,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A43,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK43" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A43,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A43,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL43" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A43,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A43,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM43" s="9" t="n">
@@ -7356,9 +7232,7 @@
       <c r="V44" s="9" t="n">
         <v>687</v>
       </c>
-      <c r="W44" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="W44" s="9" t="n"/>
       <c r="X44" s="9" t="n"/>
       <c r="Y44" s="9" t="n">
         <v>835</v>
@@ -7394,19 +7268,19 @@
       </c>
       <c r="AI44" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ44" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A44,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A44,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK44" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A44,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A44,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL44" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A44,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A44,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM44" s="9" t="n"/>
@@ -7511,15 +7385,9 @@
       <c r="V45" s="9" t="n">
         <v>628</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="9" t="n">
-        <v>1205</v>
-      </c>
+      <c r="W45" s="9" t="n"/>
+      <c r="X45" s="9" t="n"/>
+      <c r="Y45" s="9" t="n"/>
       <c r="Z45" s="9" t="inlineStr">
         <is>
           <t>fanhourbr</t>
@@ -7546,18 +7414,24 @@
         <v>119</v>
       </c>
       <c r="AG45" s="9" t="n"/>
-      <c r="AH45" s="9" t="n"/>
-      <c r="AI45" s="9" t="n"/>
+      <c r="AH45" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI45" s="9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="AJ45" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A45,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A45,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK45" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A45,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A45,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL45" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A45,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A45,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM45" s="9" t="n"/>
@@ -7658,9 +7532,7 @@
       <c r="V46" s="9" t="n">
         <v>435</v>
       </c>
-      <c r="W46" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="W46" s="9" t="n"/>
       <c r="X46" s="9" t="n"/>
       <c r="Y46" s="9" t="n">
         <v>818</v>
@@ -7696,19 +7568,19 @@
       </c>
       <c r="AI46" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ46" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A46,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A46,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK46" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A46,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A46,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL46" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A46,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A46,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM46" s="9" t="n"/>
@@ -7849,19 +7721,19 @@
       </c>
       <c r="AI47" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ47" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A47,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A47,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK47" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A47,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A47,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL47" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A47,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A47,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM47" s="9" t="n">
@@ -8002,15 +7874,15 @@
         </is>
       </c>
       <c r="AJ48" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A48,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A48,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK48" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A48,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A48,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL48" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A48,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A48,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM48" s="9" t="n">
@@ -8117,15 +7989,9 @@
       <c r="V49" s="9" t="n">
         <v>820</v>
       </c>
-      <c r="W49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="9" t="n">
-        <v>1083</v>
-      </c>
+      <c r="W49" s="9" t="n"/>
+      <c r="X49" s="9" t="n"/>
+      <c r="Y49" s="9" t="n"/>
       <c r="Z49" s="9" t="inlineStr">
         <is>
           <t>omniverselivraria</t>
@@ -8155,15 +8021,15 @@
       <c r="AH49" s="9" t="n"/>
       <c r="AI49" s="9" t="n"/>
       <c r="AJ49" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A49,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A49,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK49" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A49,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A49,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL49" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A49,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A49,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM49" s="9" t="n">
@@ -8274,15 +8140,9 @@
       <c r="V50" s="9" t="n">
         <v>566</v>
       </c>
-      <c r="W50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="9" t="n">
-        <v>1744</v>
-      </c>
+      <c r="W50" s="9" t="n"/>
+      <c r="X50" s="9" t="n"/>
+      <c r="Y50" s="9" t="n"/>
       <c r="Z50" s="9" t="inlineStr">
         <is>
           <t>pittasboardgames</t>
@@ -8312,15 +8172,15 @@
       <c r="AH50" s="9" t="n"/>
       <c r="AI50" s="9" t="n"/>
       <c r="AJ50" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A50,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A50,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK50" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A50,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A50,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL50" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A50,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A50,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM50" s="9" t="n">
@@ -8424,9 +8284,7 @@
       <c r="U51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="9" t="n">
-        <v>4310</v>
-      </c>
+      <c r="V51" s="9" t="n"/>
       <c r="W51" s="9" t="n"/>
       <c r="X51" s="9" t="n"/>
       <c r="Y51" s="9" t="n">
@@ -8459,23 +8317,23 @@
       </c>
       <c r="AG51" s="9" t="n"/>
       <c r="AH51" s="9" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AI51" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ51" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A51,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A51,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK51" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A51,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A51,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL51" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A51,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A51,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM51" s="9" t="n">
@@ -8586,12 +8444,8 @@
       <c r="V52" s="9" t="n">
         <v>563</v>
       </c>
-      <c r="W52" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X52" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="W52" s="9" t="n"/>
+      <c r="X52" s="9" t="n"/>
       <c r="Y52" s="9" t="n">
         <v>484</v>
       </c>
@@ -8626,19 +8480,19 @@
       </c>
       <c r="AI52" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ52" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A52,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A52,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK52" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A52,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A52,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL52" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A52,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A52,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM52" s="9" t="n">
@@ -8742,15 +8596,9 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>1527</v>
-      </c>
-      <c r="W53" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X53" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="V53" s="9" t="n"/>
+      <c r="W53" s="9" t="n"/>
+      <c r="X53" s="9" t="n"/>
       <c r="Y53" s="9" t="n">
         <v>305</v>
       </c>
@@ -8783,23 +8631,23 @@
         </is>
       </c>
       <c r="AH53" s="9" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AI53" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ53" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A53,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A53,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK53" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A53,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A53,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL53" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A53,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A53,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM53" s="9" t="n">
@@ -8906,15 +8754,9 @@
       <c r="V54" s="9" t="n">
         <v>364</v>
       </c>
-      <c r="W54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="9" t="n">
-        <v>1486</v>
-      </c>
+      <c r="W54" s="9" t="n"/>
+      <c r="X54" s="9" t="n"/>
+      <c r="Y54" s="9" t="n"/>
       <c r="Z54" s="9" t="inlineStr">
         <is>
           <t>xplaceoficial</t>
@@ -8944,15 +8786,15 @@
       <c r="AH54" s="9" t="n"/>
       <c r="AI54" s="9" t="n"/>
       <c r="AJ54" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A54,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A54,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK54" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A54,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A54,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL54" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A54,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A54,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM54" s="9" t="n"/>
@@ -9047,9 +8889,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n"/>
-      <c r="W55" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="W55" s="9" t="n"/>
       <c r="X55" s="9" t="n"/>
       <c r="Y55" s="9" t="n">
         <v>926</v>
@@ -9081,23 +8921,23 @@
       </c>
       <c r="AG55" s="9" t="n"/>
       <c r="AH55" s="9" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AI55" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ55" s="12">
-        <f>IFERROR(INDEX(cesta!$O$2:$O$37,MATCH($A55,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$O$2:$O$43,MATCH($A55,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AK55" s="12">
-        <f>IFERROR(INDEX(cesta!$P$2:$P$37,MATCH($A55,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$P$2:$P$43,MATCH($A55,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AL55" s="12">
-        <f>IFERROR(INDEX(cesta!$Q$2:$Q$37,MATCH($A55,cesta!$A$2:$A$37,0)),"")</f>
+        <f>IFERROR(INDEX(cesta!$Q$2:$Q$43,MATCH($A55,cesta!$A$2:$A$43,0)),"")</f>
         <v/>
       </c>
       <c r="AM55" s="9" t="n"/>
@@ -9758,7 +9598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W37"/>
+  <dimension ref="A1:W43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9924,18 +9764,12 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
       <c r="I2" s="12" t="n">
         <v>12</v>
       </c>
@@ -9955,15 +9789,15 @@
         <v>43.5</v>
       </c>
       <c r="O2" s="12">
-        <f>IF(OR(I2="",L2=""),"",F2+I2+L2)</f>
+        <f>IF(OR(F2="",I2="",L2=""),"",F2+I2+L2)</f>
         <v/>
       </c>
       <c r="P2" s="12">
-        <f>IF(OR(J2="",M2=""),"",G2+J2+M2)</f>
+        <f>IF(OR(G2="",J2="",M2=""),"",G2+J2+M2)</f>
         <v/>
       </c>
       <c r="Q2" s="12">
-        <f>IF(OR(K2="",N2=""),"",H2+K2+N2)</f>
+        <f>IF(OR(H2="",K2="",N2=""),"",H2+K2+N2)</f>
         <v/>
       </c>
       <c r="R2" s="12" t="n">
@@ -10037,15 +9871,15 @@
         <v>55</v>
       </c>
       <c r="O3" s="12">
-        <f>IF(OR(I3="",L3=""),"",F3+I3+L3)</f>
+        <f>IF(OR(F3="",I3="",L3=""),"",F3+I3+L3)</f>
         <v/>
       </c>
       <c r="P3" s="12">
-        <f>IF(OR(J3="",M3=""),"",G3+J3+M3)</f>
+        <f>IF(OR(G3="",J3="",M3=""),"",G3+J3+M3)</f>
         <v/>
       </c>
       <c r="Q3" s="12">
-        <f>IF(OR(K3="",N3=""),"",H3+K3+N3)</f>
+        <f>IF(OR(H3="",K3="",N3=""),"",H3+K3+N3)</f>
         <v/>
       </c>
       <c r="R3" s="12" t="n">
@@ -10068,12 +9902,12 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>ChIJ-17ZQDG9pgARc-AxpXmaNRU</t>
+          <t>ChIJsUAT-dObpgARCT2C5QpnVKU</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>La Tabuleria</t>
+          <t>Garagem do Nerd</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -10082,7 +9916,7 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
@@ -10090,74 +9924,52 @@
         </is>
       </c>
       <c r="F4" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="J4" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L4" s="12" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="M4" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="N4" s="12" t="n">
-        <v>41.5</v>
-      </c>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="12" t="n"/>
+      <c r="M4" s="12" t="n"/>
+      <c r="N4" s="12" t="n"/>
       <c r="O4" s="12">
-        <f>IF(OR(I4="",L4=""),"",F4+I4+L4)</f>
+        <f>IF(OR(F4="",I4="",L4=""),"",F4+I4+L4)</f>
         <v/>
       </c>
       <c r="P4" s="12">
-        <f>IF(OR(J4="",M4=""),"",G4+J4+M4)</f>
+        <f>IF(OR(G4="",J4="",M4=""),"",G4+J4+M4)</f>
         <v/>
       </c>
       <c r="Q4" s="12">
-        <f>IF(OR(K4="",N4=""),"",H4+K4+N4)</f>
-        <v/>
-      </c>
-      <c r="R4" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="S4" s="12" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="T4" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="U4" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V4" s="12" t="n">
-        <v>25</v>
-      </c>
+        <f>IF(OR(H4="",K4="",N4=""),"",H4+K4+N4)</f>
+        <v/>
+      </c>
+      <c r="R4" s="12" t="n"/>
+      <c r="S4" s="12" t="n"/>
+      <c r="T4" s="12" t="n"/>
+      <c r="U4" s="12" t="n"/>
+      <c r="V4" s="12" t="n"/>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2024-06-23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>ChIJ6ZLMZw-XpgAR_OR6SwY5xKo</t>
+          <t>ChIJ-17ZQDG9pgARc-AxpXmaNRU</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Shelf Bar e Jogos</t>
+          <t>La Tabuleria</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -10166,7 +9978,7 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
@@ -10174,58 +9986,58 @@
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>20</v>
       </c>
       <c r="H5" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="N5" s="12" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="O5" s="12">
+        <f>IF(OR(F5="",I5="",L5=""),"",F5+I5+L5)</f>
+        <v/>
+      </c>
+      <c r="P5" s="12">
+        <f>IF(OR(G5="",J5="",M5=""),"",G5+J5+M5)</f>
+        <v/>
+      </c>
+      <c r="Q5" s="12">
+        <f>IF(OR(H5="",K5="",N5=""),"",H5+K5+N5)</f>
+        <v/>
+      </c>
+      <c r="R5" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="S5" s="12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="T5" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U5" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="V5" s="12" t="n">
         <v>25</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="M5" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="N5" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="O5" s="12">
-        <f>IF(OR(I5="",L5=""),"",F5+I5+L5)</f>
-        <v/>
-      </c>
-      <c r="P5" s="12">
-        <f>IF(OR(J5="",M5=""),"",G5+J5+M5)</f>
-        <v/>
-      </c>
-      <c r="Q5" s="12">
-        <f>IF(OR(K5="",N5=""),"",H5+K5+N5)</f>
-        <v/>
-      </c>
-      <c r="R5" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="S5" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="T5" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="U5" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="V5" s="12" t="n">
-        <v>28</v>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -10236,21 +10048,21 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>ChIJ-97tiEeNpJIRb_eV7a-sxBs</t>
+          <t>ChIJx5jr3zGXpgARQGx9eX7TDmY</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Ludoteca Sidequest</t>
+          <t>LudoCafé</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Belém</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
@@ -10258,234 +10070,234 @@
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>24.25</v>
+        <v>18.75</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>25.5</v>
+        <v>22.5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>26.75</v>
+        <v>26.25</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>10</v>
+        <v>31.4</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>13</v>
+        <v>34.4</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>14.5</v>
+        <v>35.9</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>22.5</v>
+        <v>37.9</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>35</v>
+        <v>38.9</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="O6" s="12">
-        <f>IF(OR(I6="",L6=""),"",F6+I6+L6)</f>
+        <f>IF(OR(F6="",I6="",L6=""),"",F6+I6+L6)</f>
         <v/>
       </c>
       <c r="P6" s="12">
-        <f>IF(OR(J6="",M6=""),"",G6+J6+M6)</f>
+        <f>IF(OR(G6="",J6="",M6=""),"",G6+J6+M6)</f>
         <v/>
       </c>
       <c r="Q6" s="12">
-        <f>IF(OR(K6="",N6=""),"",H6+K6+N6)</f>
-        <v/>
-      </c>
-      <c r="R6" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="S6" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="T6" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="U6" s="12" t="n">
-        <v>7</v>
-      </c>
+        <f>IF(OR(H6="",K6="",N6=""),"",H6+K6+N6)</f>
+        <v/>
+      </c>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="12" t="n"/>
+      <c r="T6" s="12" t="n"/>
+      <c r="U6" s="12" t="n"/>
       <c r="V6" s="12" t="n">
-        <v>13</v>
+        <v>38.9</v>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2024-06-23, 2024-11-16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>ChIJyXjE650xWpMRJL-J6QbGkt4</t>
+          <t>ChIJ6ZLMZw-XpgAR_OR6SwY5xKo</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>FORTALÚDICA - BURGERS &amp; JOGOS</t>
+          <t>Shelf Bar e Jogos</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Brasília</t>
+          <t>Belo Horizonte</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>8.5</v>
+        <v>25</v>
       </c>
       <c r="K7" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L7" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="N7" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="O7" s="12">
+        <f>IF(OR(F7="",I7="",L7=""),"",F7+I7+L7)</f>
+        <v/>
+      </c>
+      <c r="P7" s="12">
+        <f>IF(OR(G7="",J7="",M7=""),"",G7+J7+M7)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="12">
+        <f>IF(OR(H7="",K7="",N7=""),"",H7+K7+N7)</f>
+        <v/>
+      </c>
+      <c r="R7" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="S7" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="T7" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="U7" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L7" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="M7" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="N7" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="O7" s="12">
-        <f>IF(OR(I7="",L7=""),"",F7+I7+L7)</f>
-        <v/>
-      </c>
-      <c r="P7" s="12">
-        <f>IF(OR(J7="",M7=""),"",G7+J7+M7)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="12">
-        <f>IF(OR(K7="",N7=""),"",H7+K7+N7)</f>
-        <v/>
-      </c>
-      <c r="R7" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="S7" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="T7" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="V7" s="12" t="n"/>
+      <c r="V7" s="12" t="n">
+        <v>28</v>
+      </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>ChIJdUv4La46WpMRnBvNknmOqWo</t>
+          <t>ChIJ-97tiEeNpJIRb_eV7a-sxBs</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Inside Games</t>
+          <t>Ludoteca Sidequest</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Brasília</t>
+          <t>Belém</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>0</v>
+        <v>24.25</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>0</v>
+        <v>26.75</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="O8" s="12">
-        <f>IF(OR(I8="",L8=""),"",F8+I8+L8)</f>
+        <f>IF(OR(F8="",I8="",L8=""),"",F8+I8+L8)</f>
         <v/>
       </c>
       <c r="P8" s="12">
-        <f>IF(OR(J8="",M8=""),"",G8+J8+M8)</f>
+        <f>IF(OR(G8="",J8="",M8=""),"",G8+J8+M8)</f>
         <v/>
       </c>
       <c r="Q8" s="12">
-        <f>IF(OR(K8="",N8=""),"",H8+K8+N8)</f>
-        <v/>
-      </c>
-      <c r="R8" s="12" t="n"/>
-      <c r="S8" s="12" t="n"/>
+        <f>IF(OR(H8="",K8="",N8=""),"",H8+K8+N8)</f>
+        <v/>
+      </c>
+      <c r="R8" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="S8" s="12" t="n">
+        <v>30.5</v>
+      </c>
       <c r="T8" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="U8" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V8" s="12" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="V8" s="12" t="n">
+        <v>13</v>
+      </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>ChIJzdFNP3AyWpMRH2P6HEuhE-I</t>
+          <t>ChIJyXjE650xWpMRJL-J6QbGkt4</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Loja de Jogos - Asgard</t>
+          <t>FORTALÚDICA - BURGERS &amp; JOGOS</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -10494,82 +10306,74 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>21.25</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n">
-        <v>11.25</v>
+        <v>7</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>17</v>
+        <v>8.5</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>21.25</v>
+        <v>12</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>29.5</v>
+        <v>25</v>
       </c>
       <c r="M9" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="N9" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="N9" s="12" t="n">
-        <v>39</v>
-      </c>
       <c r="O9" s="12">
-        <f>IF(OR(I9="",L9=""),"",F9+I9+L9)</f>
+        <f>IF(OR(F9="",I9="",L9=""),"",F9+I9+L9)</f>
         <v/>
       </c>
       <c r="P9" s="12">
-        <f>IF(OR(J9="",M9=""),"",G9+J9+M9)</f>
+        <f>IF(OR(G9="",J9="",M9=""),"",G9+J9+M9)</f>
         <v/>
       </c>
       <c r="Q9" s="12">
-        <f>IF(OR(K9="",N9=""),"",H9+K9+N9)</f>
+        <f>IF(OR(H9="",K9="",N9=""),"",H9+K9+N9)</f>
         <v/>
       </c>
       <c r="R9" s="12" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="S9" s="12" t="n">
-        <v>30.5</v>
+        <v>15</v>
       </c>
       <c r="T9" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="U9" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V9" s="12" t="n">
-        <v>22</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="V9" s="12" t="n"/>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2025-12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>ChIJ15nLgwAwWpMRY1whwD29ZSo</t>
+          <t>ChIJdUv4La46WpMRnBvNknmOqWo</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Ludoteca BGC</t>
+          <t>Inside Games</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -10578,78 +10382,70 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>30</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>13.75</v>
+        <v>9.5</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>29.25</v>
+        <v>6</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="O10" s="12">
-        <f>IF(OR(I10="",L10=""),"",F10+I10+L10)</f>
+        <f>IF(OR(F10="",I10="",L10=""),"",F10+I10+L10)</f>
         <v/>
       </c>
       <c r="P10" s="12">
-        <f>IF(OR(J10="",M10=""),"",G10+J10+M10)</f>
+        <f>IF(OR(G10="",J10="",M10=""),"",G10+J10+M10)</f>
         <v/>
       </c>
       <c r="Q10" s="12">
-        <f>IF(OR(K10="",N10=""),"",H10+K10+N10)</f>
+        <f>IF(OR(H10="",K10="",N10=""),"",H10+K10+N10)</f>
         <v/>
       </c>
       <c r="R10" s="12" t="n"/>
       <c r="S10" s="12" t="n"/>
       <c r="T10" s="12" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="U10" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V10" s="12" t="n">
-        <v>14</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="V10" s="12" t="n"/>
       <c r="W10" s="9" t="inlineStr">
         <is>
-          <t>2019-03, 2025-03, 2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>ChIJN8BZeb85WpMRgVKT05caxB4</t>
+          <t>ChIJzdFNP3AyWpMRH2P6HEuhE-I</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Utopia Games &amp; Food</t>
+          <t>Loja de Jogos - Asgard</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -10658,63 +10454,67 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0</v>
+        <v>21.25</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>5</v>
+        <v>11.25</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>9.5</v>
+        <v>21.25</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>50</v>
+        <v>29.5</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="O11" s="12">
-        <f>IF(OR(I11="",L11=""),"",F11+I11+L11)</f>
+        <f>IF(OR(F11="",I11="",L11=""),"",F11+I11+L11)</f>
         <v/>
       </c>
       <c r="P11" s="12">
-        <f>IF(OR(J11="",M11=""),"",G11+J11+M11)</f>
+        <f>IF(OR(G11="",J11="",M11=""),"",G11+J11+M11)</f>
         <v/>
       </c>
       <c r="Q11" s="12">
-        <f>IF(OR(K11="",N11=""),"",H11+K11+N11)</f>
-        <v/>
-      </c>
-      <c r="R11" s="12" t="n"/>
+        <f>IF(OR(H11="",K11="",N11=""),"",H11+K11+N11)</f>
+        <v/>
+      </c>
+      <c r="R11" s="12" t="n">
+        <v>45</v>
+      </c>
       <c r="S11" s="12" t="n">
-        <v>25.5</v>
+        <v>30.5</v>
       </c>
       <c r="T11" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U11" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="V11" s="12" t="n"/>
+      <c r="V11" s="12" t="n">
+        <v>22</v>
+      </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>sem data</t>
@@ -10724,157 +10524,151 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>ChIJ3ekLtDjl3JQRHwtNgmINgLo</t>
+          <t>ChIJ15nLgwAwWpMRY1whwD29ZSo</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Alçapão Jogos</t>
+          <t>Ludoteca BGC</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Brasília</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>10</v>
+        <v>5.25</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>12</v>
+        <v>29.25</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="O12" s="12">
-        <f>IF(OR(I12="",L12=""),"",F12+I12+L12)</f>
+        <f>IF(OR(F12="",I12="",L12=""),"",F12+I12+L12)</f>
         <v/>
       </c>
       <c r="P12" s="12">
-        <f>IF(OR(J12="",M12=""),"",G12+J12+M12)</f>
+        <f>IF(OR(G12="",J12="",M12=""),"",G12+J12+M12)</f>
         <v/>
       </c>
       <c r="Q12" s="12">
-        <f>IF(OR(K12="",N12=""),"",H12+K12+N12)</f>
+        <f>IF(OR(H12="",K12="",N12=""),"",H12+K12+N12)</f>
         <v/>
       </c>
       <c r="R12" s="12" t="n"/>
       <c r="S12" s="12" t="n"/>
-      <c r="T12" s="12" t="n"/>
+      <c r="T12" s="12" t="n">
+        <v>8.5</v>
+      </c>
       <c r="U12" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="V12" s="12" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="V12" s="12" t="n">
+        <v>14</v>
+      </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2019-03, 2025-03, 2026-08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>ChIJY_lqHVLl3JQRvDHacOMDKuc</t>
+          <t>ChIJN8BZeb85WpMRgVKT05caxB4</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>BoardZ Game Pub</t>
+          <t>Utopia Games &amp; Food</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Curitiba</t>
+          <t>Brasília</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>25</v>
+        <v>9.5</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="O13" s="12">
-        <f>IF(OR(I13="",L13=""),"",F13+I13+L13)</f>
+        <f>IF(OR(F13="",I13="",L13=""),"",F13+I13+L13)</f>
         <v/>
       </c>
       <c r="P13" s="12">
-        <f>IF(OR(J13="",M13=""),"",G13+J13+M13)</f>
+        <f>IF(OR(G13="",J13="",M13=""),"",G13+J13+M13)</f>
         <v/>
       </c>
       <c r="Q13" s="12">
-        <f>IF(OR(K13="",N13=""),"",H13+K13+N13)</f>
-        <v/>
-      </c>
-      <c r="R13" s="12" t="n">
-        <v>32</v>
-      </c>
+        <f>IF(OR(H13="",K13="",N13=""),"",H13+K13+N13)</f>
+        <v/>
+      </c>
+      <c r="R13" s="12" t="n"/>
       <c r="S13" s="12" t="n">
-        <v>32</v>
+        <v>25.5</v>
       </c>
       <c r="T13" s="12" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U13" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V13" s="12" t="n">
-        <v>24</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="V13" s="12" t="n"/>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>sem data</t>
@@ -10884,805 +10678,723 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>ChIJawIVeV0JM0oR5BtnD_poQeA</t>
+          <t>ChIJ3ekLtDjl3JQRHwtNgmINgLo</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>CCG Floripa</t>
+          <t>Alçapão Jogos</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Florianópolis</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="N14" s="12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O14" s="12">
+        <f>IF(OR(F14="",I14="",L14=""),"",F14+I14+L14)</f>
+        <v/>
+      </c>
+      <c r="P14" s="12">
+        <f>IF(OR(G14="",J14="",M14=""),"",G14+J14+M14)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="12">
+        <f>IF(OR(H14="",K14="",N14=""),"",H14+K14+N14)</f>
+        <v/>
+      </c>
+      <c r="R14" s="12" t="n"/>
+      <c r="S14" s="12" t="n"/>
+      <c r="T14" s="12" t="n"/>
+      <c r="U14" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="N14" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="O14" s="12">
-        <f>IF(OR(I14="",L14=""),"",F14+I14+L14)</f>
-        <v/>
-      </c>
-      <c r="P14" s="12">
-        <f>IF(OR(J14="",M14=""),"",G14+J14+M14)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="12">
-        <f>IF(OR(K14="",N14=""),"",H14+K14+N14)</f>
-        <v/>
-      </c>
-      <c r="R14" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="S14" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="T14" s="12" t="n"/>
-      <c r="U14" s="12" t="n"/>
       <c r="V14" s="12" t="n"/>
       <c r="W14" s="9" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>ChIJc3F7ka83J5URQZ1XTl-_iak</t>
+          <t>ChIJY_lqHVLl3JQRvDHacOMDKuc</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Chef on Play</t>
+          <t>BoardZ Game Pub</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Florianópolis</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n">
-        <v>6.5</v>
+        <v>15</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>8.699999999999999</v>
+        <v>25</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>21.9</v>
+        <v>26.75</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>25.9</v>
+        <v>28</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>28.9</v>
+        <v>32</v>
       </c>
       <c r="O15" s="12">
-        <f>IF(OR(I15="",L15=""),"",F15+I15+L15)</f>
+        <f>IF(OR(F15="",I15="",L15=""),"",F15+I15+L15)</f>
         <v/>
       </c>
       <c r="P15" s="12">
-        <f>IF(OR(J15="",M15=""),"",G15+J15+M15)</f>
+        <f>IF(OR(G15="",J15="",M15=""),"",G15+J15+M15)</f>
         <v/>
       </c>
       <c r="Q15" s="12">
-        <f>IF(OR(K15="",N15=""),"",H15+K15+N15)</f>
+        <f>IF(OR(H15="",K15="",N15=""),"",H15+K15+N15)</f>
         <v/>
       </c>
       <c r="R15" s="12" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="S15" s="12" t="n"/>
-      <c r="T15" s="12" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="S15" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="T15" s="12" t="n">
+        <v>15</v>
+      </c>
       <c r="U15" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V15" s="12" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="V15" s="12" t="n">
+        <v>24</v>
+      </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
-          <t>2022-12, 2024-01, 2025-04</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>ChIJJz8-gcY3J5URYdZrEXdHaAk</t>
+          <t>ChIJOczn8z7l3JQRNBEL_ZJ3iQo</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Cineplay- Restaurante e Jogos</t>
+          <t>Joyjoy Café</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Florianópolis</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="N16" s="12" t="n">
-        <v>46.77</v>
-      </c>
+        <v>13.75</v>
+      </c>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="12" t="n"/>
+      <c r="N16" s="12" t="n"/>
       <c r="O16" s="12">
-        <f>IF(OR(I16="",L16=""),"",F16+I16+L16)</f>
+        <f>IF(OR(F16="",I16="",L16=""),"",F16+I16+L16)</f>
         <v/>
       </c>
       <c r="P16" s="12">
-        <f>IF(OR(J16="",M16=""),"",G16+J16+M16)</f>
+        <f>IF(OR(G16="",J16="",M16=""),"",G16+J16+M16)</f>
         <v/>
       </c>
       <c r="Q16" s="12">
-        <f>IF(OR(K16="",N16=""),"",H16+K16+N16)</f>
-        <v/>
-      </c>
-      <c r="R16" s="12" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="S16" s="12" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="T16" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="U16" s="12" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="V16" s="12" t="n">
-        <v>20.9</v>
-      </c>
+        <f>IF(OR(H16="",K16="",N16=""),"",H16+K16+N16)</f>
+        <v/>
+      </c>
+      <c r="R16" s="12" t="n"/>
+      <c r="S16" s="12" t="n"/>
+      <c r="T16" s="12" t="n"/>
+      <c r="U16" s="12" t="n"/>
+      <c r="V16" s="12" t="n"/>
       <c r="W16" s="9" t="inlineStr">
         <is>
-          <t>2022-10, 2023-05, 2023-09, 2024-06</t>
+          <t>2024-08-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>ChIJ0yXbI35IxwcR0_jLi-uINUU</t>
+          <t>ChIJawIVeV0JM0oR5BtnD_poQeA</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Balboa's Hobby Games</t>
+          <t>CCG Floripa</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Florianópolis</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="M17" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="O17" s="12">
-        <f>IF(OR(I17="",L17=""),"",F17+I17+L17)</f>
+        <f>IF(OR(F17="",I17="",L17=""),"",F17+I17+L17)</f>
         <v/>
       </c>
       <c r="P17" s="12">
-        <f>IF(OR(J17="",M17=""),"",G17+J17+M17)</f>
+        <f>IF(OR(G17="",J17="",M17=""),"",G17+J17+M17)</f>
         <v/>
       </c>
       <c r="Q17" s="12">
-        <f>IF(OR(K17="",N17=""),"",H17+K17+N17)</f>
+        <f>IF(OR(H17="",K17="",N17=""),"",H17+K17+N17)</f>
         <v/>
       </c>
       <c r="R17" s="12" t="n">
-        <v>29.5</v>
+        <v>36</v>
       </c>
       <c r="S17" s="12" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="T17" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="U17" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V17" s="12" t="n">
-        <v>15</v>
-      </c>
+        <v>44.5</v>
+      </c>
+      <c r="T17" s="12" t="n"/>
+      <c r="U17" s="12" t="n"/>
+      <c r="V17" s="12" t="n"/>
       <c r="W17" s="9" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2023-07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>ChIJHSDPTgF5GZURKmSqKITyoGM</t>
+          <t>ChIJc3F7ka83J5URQZ1XTl-_iak</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Arcadea Gaming Pub</t>
+          <t>Chef on Play</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Porto Alegre</t>
+          <t>Florianópolis</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n">
-        <v>17.75</v>
+        <v>6.5</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>39</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>35</v>
+        <v>23.9</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>40</v>
+        <v>25.9</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>45</v>
+        <v>34.9</v>
       </c>
       <c r="O18" s="12">
-        <f>IF(OR(I18="",L18=""),"",F18+I18+L18)</f>
+        <f>IF(OR(F18="",I18="",L18=""),"",F18+I18+L18)</f>
         <v/>
       </c>
       <c r="P18" s="12">
-        <f>IF(OR(J18="",M18=""),"",G18+J18+M18)</f>
+        <f>IF(OR(G18="",J18="",M18=""),"",G18+J18+M18)</f>
         <v/>
       </c>
       <c r="Q18" s="12">
-        <f>IF(OR(K18="",N18=""),"",H18+K18+N18)</f>
+        <f>IF(OR(H18="",K18="",N18=""),"",H18+K18+N18)</f>
         <v/>
       </c>
       <c r="R18" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="S18" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="T18" s="12" t="n">
-        <v>19</v>
-      </c>
+        <v>25.9</v>
+      </c>
+      <c r="S18" s="12" t="n"/>
+      <c r="T18" s="12" t="n"/>
       <c r="U18" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V18" s="12" t="n">
-        <v>29</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="V18" s="12" t="n"/>
       <c r="W18" s="9" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2022-12, 2024-01, 2025-04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>ChIJ41pgHNFDGZURC7yTegyn7nU</t>
+          <t>ChIJJz8-gcY3J5URYdZrEXdHaAk</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Toca do Rato - Pizzaria e Jogos de Tabuleiro</t>
+          <t>Cineplay- Restaurante e Jogos</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Porto Alegre</t>
+          <t>Florianópolis</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>7.5</v>
+        <v>17.9</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>10</v>
+        <v>20.9</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>57.17</v>
+        <v>26.55</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>64.45</v>
+        <v>31.9</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>71.5</v>
+        <v>50.52</v>
       </c>
       <c r="O19" s="12">
-        <f>IF(OR(I19="",L19=""),"",F19+I19+L19)</f>
+        <f>IF(OR(F19="",I19="",L19=""),"",F19+I19+L19)</f>
         <v/>
       </c>
       <c r="P19" s="12">
-        <f>IF(OR(J19="",M19=""),"",G19+J19+M19)</f>
+        <f>IF(OR(G19="",J19="",M19=""),"",G19+J19+M19)</f>
         <v/>
       </c>
       <c r="Q19" s="12">
-        <f>IF(OR(K19="",N19=""),"",H19+K19+N19)</f>
-        <v/>
-      </c>
-      <c r="R19" s="12" t="n"/>
-      <c r="S19" s="12" t="n"/>
-      <c r="T19" s="12" t="n"/>
+        <f>IF(OR(H19="",K19="",N19=""),"",H19+K19+N19)</f>
+        <v/>
+      </c>
+      <c r="R19" s="12" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="S19" s="12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="T19" s="12" t="n">
+        <v>17</v>
+      </c>
       <c r="U19" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V19" s="12" t="n"/>
+        <v>6.75</v>
+      </c>
+      <c r="V19" s="12" t="n">
+        <v>21.4</v>
+      </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2022-10, 2023-05, 2023-09, 2024-06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>ChIJRUjwU66WoGgRzc9yJU7jkwM</t>
+          <t>ChIJ0yXbI35IxwcR0_jLi-uINUU</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Nala Land - Bar de Jogos de Tabuleiro em Recife</t>
+          <t>Balboa's Hobby Games</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Recife</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O20" s="12">
-        <f>IF(OR(I20="",L20=""),"",F20+I20+L20)</f>
+        <f>IF(OR(F20="",I20="",L20=""),"",F20+I20+L20)</f>
         <v/>
       </c>
       <c r="P20" s="12">
-        <f>IF(OR(J20="",M20=""),"",G20+J20+M20)</f>
+        <f>IF(OR(G20="",J20="",M20=""),"",G20+J20+M20)</f>
         <v/>
       </c>
       <c r="Q20" s="12">
-        <f>IF(OR(K20="",N20=""),"",H20+K20+N20)</f>
+        <f>IF(OR(H20="",K20="",N20=""),"",H20+K20+N20)</f>
         <v/>
       </c>
       <c r="R20" s="12" t="n">
-        <v>34</v>
+        <v>29.5</v>
       </c>
       <c r="S20" s="12" t="n">
-        <v>19</v>
+        <v>26.5</v>
       </c>
       <c r="T20" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="U20" s="12" t="n"/>
-      <c r="V20" s="12" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="U20" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V20" s="12" t="n">
+        <v>15</v>
+      </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2026-01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>ChIJ90Gs_9rVmwAReA7MnIyPLTE</t>
+          <t>ChIJHSDPTgF5GZURKmSqKITyoGM</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Luderia Carioca</t>
+          <t>Arcadea Gaming Pub</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Porto Alegre</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="O21" s="12">
-        <f>IF(OR(I21="",L21=""),"",F21+I21+L21)</f>
+        <f>IF(OR(F21="",I21="",L21=""),"",F21+I21+L21)</f>
         <v/>
       </c>
       <c r="P21" s="12">
-        <f>IF(OR(J21="",M21=""),"",G21+J21+M21)</f>
+        <f>IF(OR(G21="",J21="",M21=""),"",G21+J21+M21)</f>
         <v/>
       </c>
       <c r="Q21" s="12">
-        <f>IF(OR(K21="",N21=""),"",H21+K21+N21)</f>
+        <f>IF(OR(H21="",K21="",N21=""),"",H21+K21+N21)</f>
         <v/>
       </c>
       <c r="R21" s="12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="S21" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T21" s="12" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="U21" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="V21" s="12" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="V21" s="12" t="n">
+        <v>29</v>
+      </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2025-03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>ChIJoTlvBfMbFgcRHvuCKHBQrXQ</t>
+          <t>ChIJ41pgHNFDGZURC7yTegyn7nU</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>São Jogue - Bela Vista</t>
+          <t>Toca do Rato - Pizzaria e Jogos de Tabuleiro</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>Porto Alegre</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>16</v>
+        <v>7.5</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>24.25</v>
+        <v>57.17</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>32.5</v>
+        <v>64.45</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>37.5</v>
+        <v>71.5</v>
       </c>
       <c r="O22" s="12">
-        <f>IF(OR(I22="",L22=""),"",F22+I22+L22)</f>
+        <f>IF(OR(F22="",I22="",L22=""),"",F22+I22+L22)</f>
         <v/>
       </c>
       <c r="P22" s="12">
-        <f>IF(OR(J22="",M22=""),"",G22+J22+M22)</f>
+        <f>IF(OR(G22="",J22="",M22=""),"",G22+J22+M22)</f>
         <v/>
       </c>
       <c r="Q22" s="12">
-        <f>IF(OR(K22="",N22=""),"",H22+K22+N22)</f>
-        <v/>
-      </c>
-      <c r="R22" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="S22" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="T22" s="12" t="n">
-        <v>12</v>
-      </c>
+        <f>IF(OR(H22="",K22="",N22=""),"",H22+K22+N22)</f>
+        <v/>
+      </c>
+      <c r="R22" s="12" t="n"/>
+      <c r="S22" s="12" t="n"/>
+      <c r="T22" s="12" t="n"/>
       <c r="U22" s="12" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V22" s="12" t="n">
-        <v>28</v>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="V22" s="12" t="n"/>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>ChIJYTHwWgBbzpQRFenbJdM5cxU</t>
+          <t>ChIJRUjwU66WoGgRzc9yJU7jkwM</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Arena BG | Jogos de Tabuleiro | Hamburgueria</t>
+          <t>Nala Land - Bar de Jogos de Tabuleiro em Recife</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Recife</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="G23" s="12" t="n">
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K23" s="12" t="n">
         <v>12.5</v>
       </c>
-      <c r="H23" s="12" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="L23" s="12" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="O23" s="12">
-        <f>IF(OR(I23="",L23=""),"",F23+I23+L23)</f>
+        <f>IF(OR(F23="",I23="",L23=""),"",F23+I23+L23)</f>
         <v/>
       </c>
       <c r="P23" s="12">
-        <f>IF(OR(J23="",M23=""),"",G23+J23+M23)</f>
+        <f>IF(OR(G23="",J23="",M23=""),"",G23+J23+M23)</f>
         <v/>
       </c>
       <c r="Q23" s="12">
-        <f>IF(OR(K23="",N23=""),"",H23+K23+N23)</f>
+        <f>IF(OR(H23="",K23="",N23=""),"",H23+K23+N23)</f>
         <v/>
       </c>
       <c r="R23" s="12" t="n">
-        <v>52.5</v>
+        <v>34</v>
       </c>
       <c r="S23" s="12" t="n">
-        <v>28.5</v>
+        <v>19</v>
       </c>
       <c r="T23" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="U23" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V23" s="12" t="n">
-        <v>25</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="U23" s="12" t="n"/>
+      <c r="V23" s="12" t="n"/>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>sem data</t>
@@ -11692,159 +11404,135 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>ChIJKeHwNv5ZzpQRlmzx9rCTWdM</t>
+          <t>ChIJu1yUroF_mQAR7qxqAfxKSw4</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Bodogami Restaurante e Cafeteria</t>
+          <t>Game Of Boards</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>48.5</v>
-      </c>
+        <v>22.5</v>
+      </c>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+      <c r="N24" s="12" t="n"/>
       <c r="O24" s="12">
-        <f>IF(OR(I24="",L24=""),"",F24+I24+L24)</f>
+        <f>IF(OR(F24="",I24="",L24=""),"",F24+I24+L24)</f>
         <v/>
       </c>
       <c r="P24" s="12">
-        <f>IF(OR(J24="",M24=""),"",G24+J24+M24)</f>
+        <f>IF(OR(G24="",J24="",M24=""),"",G24+J24+M24)</f>
         <v/>
       </c>
       <c r="Q24" s="12">
-        <f>IF(OR(K24="",N24=""),"",H24+K24+N24)</f>
-        <v/>
-      </c>
-      <c r="R24" s="12" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="S24" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="T24" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="U24" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V24" s="12" t="n">
-        <v>36.5</v>
-      </c>
+        <f>IF(OR(H24="",K24="",N24=""),"",H24+K24+N24)</f>
+        <v/>
+      </c>
+      <c r="R24" s="12" t="n"/>
+      <c r="S24" s="12" t="n"/>
+      <c r="T24" s="12" t="n"/>
+      <c r="U24" s="12" t="n"/>
+      <c r="V24" s="12" t="n"/>
       <c r="W24" s="9" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>ChIJrT_EWwBZzpQRGAZzptZbtsY</t>
+          <t>ChIJ90Gs_9rVmwAReA7MnIyPLTE</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Cartola Luderia Bar</t>
+          <t>Luderia Carioca</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K25" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="N25" s="12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="O25" s="12">
+        <f>IF(OR(F25="",I25="",L25=""),"",F25+I25+L25)</f>
+        <v/>
+      </c>
+      <c r="P25" s="12">
+        <f>IF(OR(G25="",J25="",M25=""),"",G25+J25+M25)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="12">
+        <f>IF(OR(H25="",K25="",N25=""),"",H25+K25+N25)</f>
+        <v/>
+      </c>
+      <c r="R25" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L25" s="12" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="N25" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="O25" s="12">
-        <f>IF(OR(I25="",L25=""),"",F25+I25+L25)</f>
-        <v/>
-      </c>
-      <c r="P25" s="12">
-        <f>IF(OR(J25="",M25=""),"",G25+J25+M25)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="12">
-        <f>IF(OR(K25="",N25=""),"",H25+K25+N25)</f>
-        <v/>
-      </c>
-      <c r="R25" s="12" t="n"/>
       <c r="S25" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="T25" s="12" t="n"/>
-      <c r="U25" s="12" t="n"/>
-      <c r="V25" s="12" t="n">
-        <v>36</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="T25" s="12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U25" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="V25" s="12" t="n"/>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>sem data</t>
@@ -11854,80 +11542,74 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>ChIJbZRHQPRfzpQRz97-ZOg0yXA</t>
+          <t>ChIJOcVssmeDmQARZZrnWu2mnwA</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Castelos Bar &amp; Boardgames</t>
+          <t>TabuClub</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
       <c r="I26" s="12" t="n">
-        <v>16.42</v>
+        <v>18</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>28.4</v>
+        <v>25</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>37.9</v>
+        <v>29.75</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>39.15</v>
+        <v>23</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>43.4</v>
+        <v>36</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>45.65</v>
+        <v>46</v>
       </c>
       <c r="O26" s="12">
-        <f>IF(OR(I26="",L26=""),"",F26+I26+L26)</f>
+        <f>IF(OR(F26="",I26="",L26=""),"",F26+I26+L26)</f>
         <v/>
       </c>
       <c r="P26" s="12">
-        <f>IF(OR(J26="",M26=""),"",G26+J26+M26)</f>
+        <f>IF(OR(G26="",J26="",M26=""),"",G26+J26+M26)</f>
         <v/>
       </c>
       <c r="Q26" s="12">
-        <f>IF(OR(K26="",N26=""),"",H26+K26+N26)</f>
+        <f>IF(OR(H26="",K26="",N26=""),"",H26+K26+N26)</f>
         <v/>
       </c>
       <c r="R26" s="12" t="n">
-        <v>43.9</v>
+        <v>49</v>
       </c>
       <c r="S26" s="12" t="n">
-        <v>39.9</v>
+        <v>22</v>
       </c>
       <c r="T26" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="U26" s="12" t="n">
         <v>9</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>37.9</v>
+        <v>32</v>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -11938,96 +11620,90 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>ChIJF9j3OCRbzpQRkk74_QtOk_0</t>
+          <t>ChIJoTlvBfMbFgcRHvuCKHBQrXQ</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Coletivo Geek</t>
+          <t>São Jogue - Bela Vista</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Salvador</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
       <c r="I27" s="12" t="n">
-        <v>20.25</v>
+        <v>12</v>
       </c>
       <c r="J27" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="N27" s="12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="O27" s="12">
+        <f>IF(OR(F27="",I27="",L27=""),"",F27+I27+L27)</f>
+        <v/>
+      </c>
+      <c r="P27" s="12">
+        <f>IF(OR(G27="",J27="",M27=""),"",G27+J27+M27)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="12">
+        <f>IF(OR(H27="",K27="",N27=""),"",H27+K27+N27)</f>
+        <v/>
+      </c>
+      <c r="R27" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="S27" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="T27" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U27" s="12" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="V27" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="K27" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="N27" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="O27" s="12">
-        <f>IF(OR(I27="",L27=""),"",F27+I27+L27)</f>
-        <v/>
-      </c>
-      <c r="P27" s="12">
-        <f>IF(OR(J27="",M27=""),"",G27+J27+M27)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="12">
-        <f>IF(OR(K27="",N27=""),"",H27+K27+N27)</f>
-        <v/>
-      </c>
-      <c r="R27" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="S27" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="T27" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="U27" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V27" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>ChIJ7_DDAlH1zpQRJVJ0UHnItH8</t>
+          <t>ChIJYTHwWgBbzpQRFenbJdM5cxU</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Covil Game Bar</t>
+          <t>Arena BG | Jogos de Tabuleiro | Hamburgueria</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -12036,82 +11712,82 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>29</v>
+        <v>35.25</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>34</v>
+        <v>39.5</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="O28" s="12">
-        <f>IF(OR(I28="",L28=""),"",F28+I28+L28)</f>
+        <f>IF(OR(F28="",I28="",L28=""),"",F28+I28+L28)</f>
         <v/>
       </c>
       <c r="P28" s="12">
-        <f>IF(OR(J28="",M28=""),"",G28+J28+M28)</f>
+        <f>IF(OR(G28="",J28="",M28=""),"",G28+J28+M28)</f>
         <v/>
       </c>
       <c r="Q28" s="12">
-        <f>IF(OR(K28="",N28=""),"",H28+K28+N28)</f>
+        <f>IF(OR(H28="",K28="",N28=""),"",H28+K28+N28)</f>
         <v/>
       </c>
       <c r="R28" s="12" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="S28" s="12" t="n">
-        <v>50</v>
+        <v>28.5</v>
       </c>
       <c r="T28" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="U28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>21.5</v>
+        <v>25</v>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>ChIJiZJ_DnIDz5QRaVafFCXGkUE</t>
+          <t>ChIJKeHwNv5ZzpQRlmzx9rCTWdM</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Dungeon Games Store</t>
+          <t>Bodogami Restaurante e Cafeteria</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -12120,82 +11796,76 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
       <c r="I29" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>25.75</v>
+        <v>25</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>32.5</v>
+        <v>48.5</v>
       </c>
       <c r="O29" s="12">
-        <f>IF(OR(I29="",L29=""),"",F29+I29+L29)</f>
+        <f>IF(OR(F29="",I29="",L29=""),"",F29+I29+L29)</f>
         <v/>
       </c>
       <c r="P29" s="12">
-        <f>IF(OR(J29="",M29=""),"",G29+J29+M29)</f>
+        <f>IF(OR(G29="",J29="",M29=""),"",G29+J29+M29)</f>
         <v/>
       </c>
       <c r="Q29" s="12">
-        <f>IF(OR(K29="",N29=""),"",H29+K29+N29)</f>
+        <f>IF(OR(H29="",K29="",N29=""),"",H29+K29+N29)</f>
         <v/>
       </c>
       <c r="R29" s="12" t="n">
-        <v>31</v>
+        <v>49.5</v>
       </c>
       <c r="S29" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="T29" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U29" s="12" t="n">
         <v>8</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>28</v>
+        <v>36.5</v>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2025-03-19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>ChIJZz29dnVXzpQRvRh7_YKyUN4</t>
+          <t>ChIJrT_EWwBZzpQRGAZzptZbtsY</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Encounter | Jogos de Tabuleiro | Board Games</t>
+          <t>Cartola Luderia Bar</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -12204,76 +11874,70 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
       <c r="I30" s="12" t="n">
-        <v>27.9</v>
+        <v>29</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>27.9</v>
+        <v>36</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>27.9</v>
+        <v>38</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>34.9</v>
+        <v>29.75</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>39.9</v>
+        <v>39</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>48.9</v>
+        <v>40</v>
       </c>
       <c r="O30" s="12">
-        <f>IF(OR(I30="",L30=""),"",F30+I30+L30)</f>
+        <f>IF(OR(F30="",I30="",L30=""),"",F30+I30+L30)</f>
         <v/>
       </c>
       <c r="P30" s="12">
-        <f>IF(OR(J30="",M30=""),"",G30+J30+M30)</f>
+        <f>IF(OR(G30="",J30="",M30=""),"",G30+J30+M30)</f>
         <v/>
       </c>
       <c r="Q30" s="12">
-        <f>IF(OR(K30="",N30=""),"",H30+K30+N30)</f>
-        <v/>
-      </c>
-      <c r="R30" s="12" t="n">
-        <v>38</v>
-      </c>
+        <f>IF(OR(H30="",K30="",N30=""),"",H30+K30+N30)</f>
+        <v/>
+      </c>
+      <c r="R30" s="12" t="n"/>
       <c r="S30" s="12" t="n">
-        <v>24.9</v>
+        <v>68</v>
       </c>
       <c r="T30" s="12" t="n"/>
       <c r="U30" s="12" t="n"/>
-      <c r="V30" s="12" t="n"/>
+      <c r="V30" s="12" t="n">
+        <v>36</v>
+      </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>ChIJa3UsDhRczpQRPPSuDl6acO8</t>
+          <t>ChIJbZRHQPRfzpQRz97-ZOg0yXA</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Flow Games - Burgers, Cards &amp; Comunidade</t>
+          <t>Castelos Bar &amp; Boardgames</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -12282,80 +11946,76 @@
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
       <c r="I31" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>6</v>
+        <v>26.9</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>7</v>
+        <v>37.9</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>11</v>
+        <v>39.15</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>14</v>
+        <v>43.4</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>34.9</v>
+        <v>45.65</v>
       </c>
       <c r="O31" s="12">
-        <f>IF(OR(I31="",L31=""),"",F31+I31+L31)</f>
+        <f>IF(OR(F31="",I31="",L31=""),"",F31+I31+L31)</f>
         <v/>
       </c>
       <c r="P31" s="12">
-        <f>IF(OR(J31="",M31=""),"",G31+J31+M31)</f>
+        <f>IF(OR(G31="",J31="",M31=""),"",G31+J31+M31)</f>
         <v/>
       </c>
       <c r="Q31" s="12">
-        <f>IF(OR(K31="",N31=""),"",H31+K31+N31)</f>
+        <f>IF(OR(H31="",K31="",N31=""),"",H31+K31+N31)</f>
         <v/>
       </c>
       <c r="R31" s="12" t="n">
-        <v>12</v>
+        <v>43.9</v>
       </c>
       <c r="S31" s="12" t="n">
-        <v>10</v>
+        <v>39.9</v>
       </c>
       <c r="T31" s="12" t="n">
-        <v>6.5</v>
+        <v>15</v>
       </c>
       <c r="U31" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V31" s="12" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="V31" s="12" t="n">
+        <v>37.4</v>
+      </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
-          <t>2022-09, 2025-08</t>
+          <t>sem data</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>ChIJn7uU0RNbzpQRI4GI9KHOo_s</t>
+          <t>ChIJF9j3OCRbzpQRkk74_QtOk_0</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Jogasampa</t>
+          <t>Coletivo Geek</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -12364,68 +12024,76 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
       <c r="I32" s="12" t="n">
-        <v>6</v>
+        <v>20.25</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="12" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="M32" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="N32" s="12" t="n">
+        <v>39</v>
+      </c>
       <c r="O32" s="12">
-        <f>IF(OR(I32="",L32=""),"",F32+I32+L32)</f>
+        <f>IF(OR(F32="",I32="",L32=""),"",F32+I32+L32)</f>
         <v/>
       </c>
       <c r="P32" s="12">
-        <f>IF(OR(J32="",M32=""),"",G32+J32+M32)</f>
+        <f>IF(OR(G32="",J32="",M32=""),"",G32+J32+M32)</f>
         <v/>
       </c>
       <c r="Q32" s="12">
-        <f>IF(OR(K32="",N32=""),"",H32+K32+N32)</f>
-        <v/>
-      </c>
-      <c r="R32" s="12" t="n"/>
-      <c r="S32" s="12" t="n"/>
-      <c r="T32" s="12" t="n"/>
+        <f>IF(OR(H32="",K32="",N32=""),"",H32+K32+N32)</f>
+        <v/>
+      </c>
+      <c r="R32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="S32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="T32" s="12" t="n">
+        <v>22</v>
+      </c>
       <c r="U32" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V32" s="12" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="V32" s="12" t="n">
+        <v>30</v>
+      </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>ChIJTaG5ALpZzpQRUDErQ-RkfTs</t>
+          <t>ChIJ7_DDAlH1zpQRJVJ0UHnItH8</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Ludus Luderia</t>
+          <t>Covil Game Bar</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -12434,82 +12102,76 @@
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>161</v>
+        <v>71</v>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J33" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="K33" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="N33" s="12" t="n">
-        <v>56.5</v>
+        <v>38</v>
       </c>
       <c r="O33" s="12">
-        <f>IF(OR(I33="",L33=""),"",F33+I33+L33)</f>
+        <f>IF(OR(F33="",I33="",L33=""),"",F33+I33+L33)</f>
         <v/>
       </c>
       <c r="P33" s="12">
-        <f>IF(OR(J33="",M33=""),"",G33+J33+M33)</f>
+        <f>IF(OR(G33="",J33="",M33=""),"",G33+J33+M33)</f>
         <v/>
       </c>
       <c r="Q33" s="12">
-        <f>IF(OR(K33="",N33=""),"",H33+K33+N33)</f>
+        <f>IF(OR(H33="",K33="",N33=""),"",H33+K33+N33)</f>
         <v/>
       </c>
       <c r="R33" s="12" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="S33" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T33" s="12" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="U33" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>36</v>
+        <v>21.5</v>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2025-07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>ChIJkWsGmd1czpQRGLydxc29vbw</t>
+          <t>ChIJiZJ_DnIDz5QRaVafFCXGkUE</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Place Games</t>
+          <t>Dungeon Games Store</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -12518,65 +12180,61 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
       <c r="I34" s="12" t="n">
-        <v>7.18</v>
+        <v>10</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>11</v>
+        <v>25.75</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>39</v>
+        <v>32.5</v>
       </c>
       <c r="O34" s="12">
-        <f>IF(OR(I34="",L34=""),"",F34+I34+L34)</f>
+        <f>IF(OR(F34="",I34="",L34=""),"",F34+I34+L34)</f>
         <v/>
       </c>
       <c r="P34" s="12">
-        <f>IF(OR(J34="",M34=""),"",G34+J34+M34)</f>
+        <f>IF(OR(G34="",J34="",M34=""),"",G34+J34+M34)</f>
         <v/>
       </c>
       <c r="Q34" s="12">
-        <f>IF(OR(K34="",N34=""),"",H34+K34+N34)</f>
+        <f>IF(OR(H34="",K34="",N34=""),"",H34+K34+N34)</f>
         <v/>
       </c>
       <c r="R34" s="12" t="n">
-        <v>38.9</v>
+        <v>31</v>
       </c>
       <c r="S34" s="12" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="T34" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U34" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="V34" s="12" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <v>28</v>
+      </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>sem data</t>
@@ -12586,12 +12244,12 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>ChIJNcHw7jNYzpQRKRHPOrb4jEw</t>
+          <t>ChIJZz29dnVXzpQRvRh7_YKyUN4</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Play Easy</t>
+          <t>Encounter | Jogos de Tabuleiro | Board Games</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -12600,78 +12258,70 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
       <c r="I35" s="12" t="n">
-        <v>6</v>
+        <v>27.9</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>7</v>
+        <v>27.9</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>9.5</v>
+        <v>27.9</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>11</v>
+        <v>34.9</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>25</v>
+        <v>39.9</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>25</v>
+        <v>48.9</v>
       </c>
       <c r="O35" s="12">
-        <f>IF(OR(I35="",L35=""),"",F35+I35+L35)</f>
+        <f>IF(OR(F35="",I35="",L35=""),"",F35+I35+L35)</f>
         <v/>
       </c>
       <c r="P35" s="12">
-        <f>IF(OR(J35="",M35=""),"",G35+J35+M35)</f>
+        <f>IF(OR(G35="",J35="",M35=""),"",G35+J35+M35)</f>
         <v/>
       </c>
       <c r="Q35" s="12">
-        <f>IF(OR(K35="",N35=""),"",H35+K35+N35)</f>
-        <v/>
-      </c>
-      <c r="R35" s="12" t="n"/>
+        <f>IF(OR(H35="",K35="",N35=""),"",H35+K35+N35)</f>
+        <v/>
+      </c>
+      <c r="R35" s="12" t="n">
+        <v>38</v>
+      </c>
       <c r="S35" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="T35" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="U35" s="12" t="n">
-        <v>6</v>
-      </c>
+        <v>24.9</v>
+      </c>
+      <c r="T35" s="12" t="n"/>
+      <c r="U35" s="12" t="n"/>
       <c r="V35" s="12" t="n"/>
       <c r="W35" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2025-06</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>ChIJsU5BAwBRzpQRAgLVvqg68os</t>
+          <t>ChIJ_aN4OAxXzpQR0UH63sAeVCA</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Tubaleria</t>
+          <t>Fan Hour Games and Burgers</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -12680,143 +12330,583 @@
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="12" t="n"/>
-      <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>36.9</v>
+      </c>
       <c r="L36" s="12" t="n">
-        <v>35</v>
+        <v>32.2</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>48</v>
+        <v>50.9</v>
       </c>
       <c r="O36" s="12">
-        <f>IF(OR(I36="",L36=""),"",F36+I36+L36)</f>
+        <f>IF(OR(F36="",I36="",L36=""),"",F36+I36+L36)</f>
         <v/>
       </c>
       <c r="P36" s="12">
-        <f>IF(OR(J36="",M36=""),"",G36+J36+M36)</f>
+        <f>IF(OR(G36="",J36="",M36=""),"",G36+J36+M36)</f>
         <v/>
       </c>
       <c r="Q36" s="12">
-        <f>IF(OR(K36="",N36=""),"",H36+K36+N36)</f>
+        <f>IF(OR(H36="",K36="",N36=""),"",H36+K36+N36)</f>
         <v/>
       </c>
       <c r="R36" s="12" t="n">
-        <v>48</v>
+        <v>50.3</v>
       </c>
       <c r="S36" s="12" t="n">
-        <v>35</v>
+        <v>26.7</v>
       </c>
       <c r="T36" s="12" t="n"/>
       <c r="U36" s="12" t="n"/>
       <c r="V36" s="12" t="n"/>
       <c r="W36" s="9" t="inlineStr">
         <is>
-          <t>2025-12, 2026-01, 2026-03, 2026-05</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>ChIJfyav9YI9uAARjwbBqcRm2_k</t>
+          <t>ChIJa3UsDhRczpQRPPSuDl6acO8</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Café Geek Cafeteria e Ludoteca</t>
+          <t>Flow Games - Burgers, Cards &amp; Comunidade</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>não</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
       <c r="I37" s="12" t="n">
-        <v>7.75</v>
+        <v>6</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M37" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="N37" s="12" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="O37" s="12">
+        <f>IF(OR(F37="",I37="",L37=""),"",F37+I37+L37)</f>
+        <v/>
+      </c>
+      <c r="P37" s="12">
+        <f>IF(OR(G37="",J37="",M37=""),"",G37+J37+M37)</f>
+        <v/>
+      </c>
+      <c r="Q37" s="12">
+        <f>IF(OR(H37="",K37="",N37=""),"",H37+K37+N37)</f>
+        <v/>
+      </c>
+      <c r="R37" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="S37" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N37" s="12" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="O37" s="12">
-        <f>IF(OR(I37="",L37=""),"",F37+I37+L37)</f>
-        <v/>
-      </c>
-      <c r="P37" s="12">
-        <f>IF(OR(J37="",M37=""),"",G37+J37+M37)</f>
-        <v/>
-      </c>
-      <c r="Q37" s="12">
-        <f>IF(OR(K37="",N37=""),"",H37+K37+N37)</f>
-        <v/>
-      </c>
-      <c r="R37" s="12" t="n"/>
-      <c r="S37" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="T37" s="12" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="U37" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37" s="12" t="n"/>
       <c r="W37" s="9" t="inlineStr">
         <is>
+          <t>2022-09, 2025-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>ChIJn7uU0RNbzpQRI4GI9KHOo_s</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Jogasampa</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n"/>
+      <c r="G38" s="12" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="12" t="n"/>
+      <c r="N38" s="12" t="n"/>
+      <c r="O38" s="12">
+        <f>IF(OR(F38="",I38="",L38=""),"",F38+I38+L38)</f>
+        <v/>
+      </c>
+      <c r="P38" s="12">
+        <f>IF(OR(G38="",J38="",M38=""),"",G38+J38+M38)</f>
+        <v/>
+      </c>
+      <c r="Q38" s="12">
+        <f>IF(OR(H38="",K38="",N38=""),"",H38+K38+N38)</f>
+        <v/>
+      </c>
+      <c r="R38" s="12" t="n"/>
+      <c r="S38" s="12" t="n"/>
+      <c r="T38" s="12" t="n"/>
+      <c r="U38" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V38" s="12" t="n"/>
+      <c r="W38" s="9" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>ChIJTaG5ALpZzpQRUDErQ-RkfTs</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Ludus Luderia</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>161</v>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="M39" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="N39" s="12" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="O39" s="12">
+        <f>IF(OR(F39="",I39="",L39=""),"",F39+I39+L39)</f>
+        <v/>
+      </c>
+      <c r="P39" s="12">
+        <f>IF(OR(G39="",J39="",M39=""),"",G39+J39+M39)</f>
+        <v/>
+      </c>
+      <c r="Q39" s="12">
+        <f>IF(OR(H39="",K39="",N39=""),"",H39+K39+N39)</f>
+        <v/>
+      </c>
+      <c r="R39" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="S39" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="T39" s="12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="U39" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="V39" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="W39" s="9" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>ChIJkWsGmd1czpQRGLydxc29vbw</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Place Games</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="12" t="n"/>
+      <c r="H40" s="12" t="n"/>
+      <c r="I40" s="12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="L40" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M40" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="N40" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="O40" s="12">
+        <f>IF(OR(F40="",I40="",L40=""),"",F40+I40+L40)</f>
+        <v/>
+      </c>
+      <c r="P40" s="12">
+        <f>IF(OR(G40="",J40="",M40=""),"",G40+J40+M40)</f>
+        <v/>
+      </c>
+      <c r="Q40" s="12">
+        <f>IF(OR(H40="",K40="",N40=""),"",H40+K40+N40)</f>
+        <v/>
+      </c>
+      <c r="R40" s="12" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="S40" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="T40" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="U40" s="12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="V40" s="12" t="n"/>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
           <t>sem data</t>
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>ChIJNcHw7jNYzpQRKRHPOrb4jEw</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Play Easy</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n"/>
+      <c r="G41" s="12" t="n"/>
+      <c r="H41" s="12" t="n"/>
+      <c r="I41" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M41" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="N41" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="O41" s="12">
+        <f>IF(OR(F41="",I41="",L41=""),"",F41+I41+L41)</f>
+        <v/>
+      </c>
+      <c r="P41" s="12">
+        <f>IF(OR(G41="",J41="",M41=""),"",G41+J41+M41)</f>
+        <v/>
+      </c>
+      <c r="Q41" s="12">
+        <f>IF(OR(H41="",K41="",N41=""),"",H41+K41+N41)</f>
+        <v/>
+      </c>
+      <c r="R41" s="12" t="n"/>
+      <c r="S41" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="T41" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="U41" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V41" s="12" t="n"/>
+      <c r="W41" s="9" t="inlineStr">
+        <is>
+          <t>sem data</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>ChIJsU5BAwBRzpQRAgLVvqg68os</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Tubaleria</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="N42" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="O42" s="12">
+        <f>IF(OR(F42="",I42="",L42=""),"",F42+I42+L42)</f>
+        <v/>
+      </c>
+      <c r="P42" s="12">
+        <f>IF(OR(G42="",J42="",M42=""),"",G42+J42+M42)</f>
+        <v/>
+      </c>
+      <c r="Q42" s="12">
+        <f>IF(OR(H42="",K42="",N42=""),"",H42+K42+N42)</f>
+        <v/>
+      </c>
+      <c r="R42" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="S42" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="T42" s="12" t="n"/>
+      <c r="U42" s="12" t="n"/>
+      <c r="V42" s="12" t="n"/>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>2025-12, 2026-01, 2026-03, 2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>ChIJfyav9YI9uAARjwbBqcRm2_k</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Café Geek Cafeteria e Ludoteca</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="12" t="n"/>
+      <c r="H43" s="12" t="n"/>
+      <c r="I43" s="12" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M43" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N43" s="12" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="O43" s="12">
+        <f>IF(OR(F43="",I43="",L43=""),"",F43+I43+L43)</f>
+        <v/>
+      </c>
+      <c r="P43" s="12">
+        <f>IF(OR(G43="",J43="",M43=""),"",G43+J43+M43)</f>
+        <v/>
+      </c>
+      <c r="Q43" s="12">
+        <f>IF(OR(H43="",K43="",N43=""),"",H43+K43+N43)</f>
+        <v/>
+      </c>
+      <c r="R43" s="12" t="n"/>
+      <c r="S43" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="T43" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U43" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="V43" s="12" t="n"/>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>sem data</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W37"/>
+  <autoFilter ref="A1:W43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13449,7 +13539,7 @@
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Distância (m) à estação de metrô mais próxima lida; vazio = nenhuma na cidade ou leitura de outra cidade (&gt; 50 km)</t>
+          <t>Distância (m) à estação de metrô mais próxima, só até 1000 m; vazio com metro_1000m = 0: nenhuma até 1000 m</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
@@ -13476,12 +13566,12 @@
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Shoppings de porte (OSM shop=mall, área ≥ 5.000 m²) até 500 m; vazio = porte não buscado</t>
+          <t>Shoppings de porte (1.000 avaliações ou mais no Maps) até 500 m; vazio = coleta anterior a 30/10/2026 ou avaliações não lidas</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>idem + OpenStreetMap</t>
+          <t>idem</t>
         </is>
       </c>
     </row>
@@ -13503,12 +13593,12 @@
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Shoppings de porte até 1000 m; vazio = porte não buscado</t>
+          <t>Shoppings de porte até 1000 m; vazio = coleta anterior a 30/10/2026 ou avaliações não lidas</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>idem + OpenStreetMap</t>
+          <t>idem</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13620,7 @@
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Distância (m) ao shopping mais próximo lido (qualquer porte)</t>
+          <t>Distância (m) ao shopping mais próximo (qualquer porte), só até 1000 m</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
@@ -13773,7 +13863,7 @@
       </c>
       <c r="D35" s="18" t="inlineStr">
         <is>
-          <t>Linhas item × variação com preço no cardápio</t>
+          <t>Linhas de referência com preço no cardápio (uma por item, tamanho e combo à parte)</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr">
@@ -13800,7 +13890,7 @@
       </c>
       <c r="D36" s="18" t="inlineStr">
         <is>
-          <t>Há couvert ou taxa de jogo por pessoa no cardápio</t>
+          <t>Couvert ou taxa de jogo por pessoa encontrado no cardápio: sim ou não encontrado (não quer dizer que não cobra)</t>
         </is>
       </c>
       <c r="E36" s="18" t="inlineStr">
@@ -14016,7 +14106,7 @@
       </c>
       <c r="D44" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E44" s="18" t="inlineStr">
@@ -14043,7 +14133,7 @@
       </c>
       <c r="D45" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr">
@@ -14070,7 +14160,7 @@
       </c>
       <c r="D46" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
@@ -14097,7 +14187,7 @@
       </c>
       <c r="D47" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr">
@@ -14124,7 +14214,7 @@
       </c>
       <c r="D48" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E48" s="18" t="inlineStr">
@@ -14151,7 +14241,7 @@
       </c>
       <c r="D49" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr">
@@ -14178,7 +14268,7 @@
       </c>
       <c r="D50" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E50" s="18" t="inlineStr">
@@ -14205,7 +14295,7 @@
       </c>
       <c r="D51" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr">
@@ -14232,7 +14322,7 @@
       </c>
       <c r="D52" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E52" s="18" t="inlineStr">
@@ -14259,7 +14349,7 @@
       </c>
       <c r="D53" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr">
@@ -14286,7 +14376,7 @@
       </c>
       <c r="D54" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E54" s="18" t="inlineStr">
@@ -14313,7 +14403,7 @@
       </c>
       <c r="D55" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr">
@@ -14340,7 +14430,7 @@
       </c>
       <c r="D56" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E56" s="18" t="inlineStr">
@@ -14367,7 +14457,7 @@
       </c>
       <c r="D57" s="18" t="inlineStr">
         <is>
-          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; couvert 0 = sem couvert)</t>
+          <t>Preço da categoria no cardápio da casa (percentil indicado no nome; vazio = sem preço no cardápio coletado; no couvert, não encontrado, o que não quer dizer que a casa não cobra)</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr">

--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/B1_resumo_estabelecimentos.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/B1_resumo_estabelecimentos.xlsx
@@ -896,11 +896,11 @@
         </is>
       </c>
       <c r="AH2" s="9" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AI2" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="AJ2" s="12">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AI13" s="9" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>não encontrado</t>
         </is>
       </c>
       <c r="AJ13" s="12">
@@ -4850,11 +4850,11 @@
       </c>
       <c r="AG28" s="9" t="n"/>
       <c r="AH28" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI28" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="AJ28" s="12">
@@ -4993,11 +4993,11 @@
       </c>
       <c r="AG29" s="9" t="n"/>
       <c r="AH29" s="9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI29" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="AJ29" s="12">
@@ -5297,11 +5297,11 @@
       </c>
       <c r="AG31" s="9" t="n"/>
       <c r="AH31" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AI31" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="AJ31" s="12">
@@ -5742,11 +5742,11 @@
       </c>
       <c r="AG34" s="9" t="n"/>
       <c r="AH34" s="9" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI34" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="AJ34" s="12">
@@ -6954,11 +6954,11 @@
       </c>
       <c r="AG42" s="9" t="n"/>
       <c r="AH42" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AI42" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="AJ42" s="12">
@@ -7264,11 +7264,11 @@
       </c>
       <c r="AG44" s="9" t="n"/>
       <c r="AH44" s="9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI44" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="AJ44" s="12">
@@ -8317,11 +8317,11 @@
       </c>
       <c r="AG51" s="9" t="n"/>
       <c r="AH51" s="9" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AI51" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="AJ51" s="12">
@@ -8631,11 +8631,11 @@
         </is>
       </c>
       <c r="AH53" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI53" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="AJ53" s="12">
@@ -8921,11 +8921,11 @@
       </c>
       <c r="AG55" s="9" t="n"/>
       <c r="AH55" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AI55" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="AJ55" s="12">
@@ -9760,16 +9760,22 @@
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="n"/>
-      <c r="G2" s="12" t="n"/>
-      <c r="H2" s="12" t="n"/>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G2" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>22.5</v>
+      </c>
       <c r="I2" s="12" t="n">
         <v>12</v>
       </c>
@@ -9815,7 +9821,7 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -10542,18 +10548,12 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>30</v>
-      </c>
+          <t>não encontrado</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n">
         <v>5.25</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>13.75</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>29.25</v>
+        <v>29.5</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>31</v>
@@ -11274,16 +11274,22 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>5</v>
+      </c>
       <c r="I22" s="12" t="n">
         <v>7.5</v>
       </c>
@@ -11323,7 +11329,7 @@
       <c r="V22" s="12" t="n"/>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2025-10</t>
         </is>
       </c>
     </row>
@@ -11344,16 +11350,22 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G23" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>não encontrado</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
+      <c r="H23" s="12" t="n">
+        <v>25</v>
+      </c>
       <c r="I23" s="12" t="n">
         <v>11.5</v>
       </c>
@@ -11397,7 +11409,7 @@
       <c r="V23" s="12" t="n"/>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -11480,16 +11492,22 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>20</v>
+      </c>
       <c r="I25" s="12" t="n">
         <v>9</v>
       </c>
@@ -11535,7 +11553,7 @@
       <c r="V25" s="12" t="n"/>
       <c r="W25" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -11556,16 +11574,22 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>23.75</v>
+      </c>
       <c r="I26" s="12" t="n">
         <v>18</v>
       </c>
@@ -11613,7 +11637,7 @@
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2026-01</t>
         </is>
       </c>
     </row>
@@ -12102,16 +12126,22 @@
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="12" t="n"/>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>18.75</v>
+      </c>
       <c r="I33" s="12" t="n">
         <v>14</v>
       </c>
@@ -12159,7 +12189,7 @@
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2024-04, 2025-07</t>
         </is>
       </c>
     </row>
@@ -12258,16 +12288,22 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="12" t="n"/>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>41.25</v>
+      </c>
       <c r="I35" s="12" t="n">
         <v>27.9</v>
       </c>
@@ -12309,7 +12345,7 @@
       <c r="V35" s="12" t="n"/>
       <c r="W35" s="9" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-06, 2026-01</t>
         </is>
       </c>
     </row>
@@ -12632,16 +12668,22 @@
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>18.75</v>
+      </c>
       <c r="I40" s="12" t="n">
         <v>6.9</v>
       </c>
@@ -12687,7 +12729,7 @@
       <c r="V40" s="12" t="n"/>
       <c r="W40" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -12782,16 +12824,22 @@
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="n"/>
-      <c r="G42" s="12" t="n"/>
-      <c r="H42" s="12" t="n"/>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>28</v>
+      </c>
       <c r="I42" s="12" t="n"/>
       <c r="J42" s="12" t="n"/>
       <c r="K42" s="12" t="n"/>
@@ -12848,16 +12896,22 @@
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="12" t="n"/>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>12</v>
+      </c>
       <c r="I43" s="12" t="n">
         <v>7.75</v>
       </c>
@@ -12901,7 +12955,7 @@
       <c r="V43" s="12" t="n"/>
       <c r="W43" s="9" t="inlineStr">
         <is>
-          <t>sem data</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>

--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/B1_resumo_estabelecimentos.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/B1_resumo_estabelecimentos.xlsx
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI6" s="9" t="inlineStr">
         <is>
@@ -3038,11 +3038,11 @@
       </c>
       <c r="AG16" s="9" t="n"/>
       <c r="AH16" s="9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI16" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="AJ16" s="12">
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
@@ -10076,13 +10076,13 @@
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>18.75</v>
+        <v>17.5</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>22.5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>26.25</v>
+        <v>27.5</v>
       </c>
       <c r="I6" s="12" t="n">
         <v>31.4</v>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>2024-06-23, 2024-11-16</t>
+          <t>2024-11-16</t>
         </is>
       </c>
     </row>
@@ -10762,16 +10762,22 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>não encontrado</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>13.75</v>
+      </c>
       <c r="I15" s="12" t="n">
         <v>15</v>
       </c>
